--- a/Backtest/02-12-24/NASDAQstock_02-12-24period252RS90.xlsx
+++ b/Backtest/02-12-24/NASDAQstock_02-12-24period252RS90.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelvinyue/Desktop/Coding project/StockAnalysis/Backtest/02-12-24/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ADCC9B7-35E0-4440-85B2-B22901B99115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="60" yWindow="500" windowWidth="28700" windowHeight="16080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -811,12 +817,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -824,8 +830,15 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -871,17 +884,25 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -919,7 +940,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -953,6 +974,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -987,9 +1009,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1162,9 +1185,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AK120"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:37">
       <c r="A1" s="1" t="s">
@@ -1284,7 +1307,7 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>92.91995148574894</v>
+        <v>92.919951485748939</v>
       </c>
       <c r="C2">
         <v>2525</v>
@@ -1296,31 +1319,31 @@
         <v>1.31</v>
       </c>
       <c r="F2">
-        <v>-1.100162811045159</v>
+        <v>-1.1001628110451589</v>
       </c>
       <c r="G2">
         <v>1.72</v>
       </c>
       <c r="H2">
-        <v>-0.919152894339218</v>
+        <v>-0.91915289433921799</v>
       </c>
       <c r="I2">
-        <v>97.20200042724609</v>
+        <v>97.202000427246091</v>
       </c>
       <c r="J2">
-        <v>93.23699989318848</v>
+        <v>93.236999893188482</v>
       </c>
       <c r="K2">
-        <v>88.52880004882813</v>
+        <v>88.528800048828131</v>
       </c>
       <c r="L2">
-        <v>69.22974988937378</v>
+        <v>69.229749889373778</v>
       </c>
       <c r="M2">
         <v>1.04</v>
       </c>
       <c r="N2">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -1335,7 +1358,7 @@
         <v>5</v>
       </c>
       <c r="T2">
-        <v>17.22222222222222</v>
+        <v>17.222222222222221</v>
       </c>
       <c r="U2" t="b">
         <v>1</v>
@@ -1386,7 +1409,7 @@
         <v>208</v>
       </c>
       <c r="AK2">
-        <v>69.44132112961489</v>
+        <v>69.441321129614892</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1412,22 +1435,22 @@
         <v>2.8</v>
       </c>
       <c r="H3">
-        <v>-0.06307977324003514</v>
+        <v>-6.3079773240035136E-2</v>
       </c>
       <c r="I3">
         <v>29.26800003051758</v>
       </c>
       <c r="J3">
-        <v>26.81950006484985</v>
+        <v>26.819500064849851</v>
       </c>
       <c r="K3">
-        <v>23.082799949646</v>
+        <v>23.082799949645999</v>
       </c>
       <c r="L3">
         <v>18.8127499961853</v>
       </c>
       <c r="M3">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="N3">
         <v>1.27</v>
@@ -1472,7 +1495,7 @@
         <v>6100</v>
       </c>
       <c r="AC3">
-        <v>256.29</v>
+        <v>256.29000000000002</v>
       </c>
       <c r="AD3">
         <v>9.09</v>
@@ -1496,7 +1519,7 @@
         <v>209</v>
       </c>
       <c r="AK3">
-        <v>58.09210615831604</v>
+        <v>58.092106158316042</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1504,43 +1527,43 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>90.78229229836265</v>
+        <v>90.782292298362648</v>
       </c>
       <c r="C4">
         <v>562</v>
       </c>
       <c r="D4">
-        <v>80.26000000000001</v>
+        <v>80.260000000000005</v>
       </c>
       <c r="E4">
         <v>2.52</v>
       </c>
       <c r="F4">
-        <v>-0.5249124545835696</v>
+        <v>-0.52491245458356961</v>
       </c>
       <c r="G4">
-        <v>2.22</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="H4">
-        <v>-0.5228227456821887</v>
+        <v>-0.52282274568218867</v>
       </c>
       <c r="I4">
-        <v>82.22800140380859</v>
+        <v>82.228001403808591</v>
       </c>
       <c r="J4">
-        <v>79.47250022888184</v>
+        <v>79.472500228881842</v>
       </c>
       <c r="K4">
-        <v>71.98980003356934</v>
+        <v>71.989800033569338</v>
       </c>
       <c r="L4">
-        <v>59.88604999542236</v>
+        <v>59.886049995422361</v>
       </c>
       <c r="M4">
         <v>1.03</v>
       </c>
       <c r="N4">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="P4">
         <v>0</v>
@@ -1614,7 +1637,7 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>96.10369921164342</v>
+        <v>96.103699211643416</v>
       </c>
       <c r="C5">
         <v>266</v>
@@ -1626,25 +1649,25 @@
         <v>2.92</v>
       </c>
       <c r="F5">
-        <v>-0.3347470474888294</v>
+        <v>-0.33474704748882939</v>
       </c>
       <c r="G5">
         <v>2.11</v>
       </c>
       <c r="H5">
-        <v>-0.6100153783867354</v>
+        <v>-0.61001537838673536</v>
       </c>
       <c r="I5">
-        <v>478.0919921875</v>
+        <v>478.09199218750001</v>
       </c>
       <c r="J5">
-        <v>445.4604995727539</v>
+        <v>445.46049957275392</v>
       </c>
       <c r="K5">
-        <v>404.3948010253906</v>
+        <v>404.39480102539062</v>
       </c>
       <c r="L5">
-        <v>328.4723999786377</v>
+        <v>328.47239997863772</v>
       </c>
       <c r="M5">
         <v>1.07</v>
@@ -1683,7 +1706,7 @@
         <v>489.69</v>
       </c>
       <c r="Z5">
-        <v>93.29000000000001</v>
+        <v>93.29</v>
       </c>
       <c r="AA5">
         <v>-41.57</v>
@@ -1716,7 +1739,7 @@
         <v>211</v>
       </c>
       <c r="AK5">
-        <v>57.37507605381057</v>
+        <v>57.375076053810567</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1724,37 +1747,37 @@
         <v>41</v>
       </c>
       <c r="B6">
-        <v>95.52759248029109</v>
+        <v>95.527592480291091</v>
       </c>
       <c r="C6">
         <v>130</v>
       </c>
       <c r="D6">
-        <v>302.4</v>
+        <v>302.39999999999998</v>
       </c>
       <c r="E6">
         <v>9.4</v>
       </c>
       <c r="F6">
-        <v>2.745932547445964</v>
+        <v>2.7459325474459639</v>
       </c>
       <c r="G6">
         <v>6.75</v>
       </c>
       <c r="H6">
-        <v>3.067928401150495</v>
+        <v>3.0679284011504948</v>
       </c>
       <c r="I6">
-        <v>303.0180053710938</v>
+        <v>303.01800537109381</v>
       </c>
       <c r="J6">
-        <v>287.9295036315918</v>
+        <v>287.92950363159179</v>
       </c>
       <c r="K6">
         <v>227.9880017089844</v>
       </c>
       <c r="L6">
-        <v>221.2361502838135</v>
+        <v>221.23615028381349</v>
       </c>
       <c r="M6">
         <v>1.05</v>
@@ -1775,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="T6">
-        <v>1.111111111111111</v>
+        <v>1.1111111111111109</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
@@ -1811,7 +1834,7 @@
         <v>100</v>
       </c>
       <c r="AF6">
-        <v>-96.90000000000001</v>
+        <v>-96.9</v>
       </c>
       <c r="AG6">
         <v>313.68</v>
@@ -1826,7 +1849,7 @@
         <v>212</v>
       </c>
       <c r="AK6">
-        <v>55.76678722871799</v>
+        <v>55.766787228717988</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1834,37 +1857,37 @@
         <v>42</v>
       </c>
       <c r="B7">
-        <v>98.81746513038206</v>
+        <v>98.817465130382061</v>
       </c>
       <c r="C7">
         <v>381</v>
       </c>
       <c r="D7">
-        <v>154.11</v>
+        <v>154.11000000000001</v>
       </c>
       <c r="E7">
         <v>4.18</v>
       </c>
       <c r="F7">
-        <v>0.2642739848596024</v>
+        <v>0.26427398485960241</v>
       </c>
       <c r="G7">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="H7">
-        <v>0.9673786132682406</v>
+        <v>0.96737861326824059</v>
       </c>
       <c r="I7">
-        <v>157.0540008544922</v>
+        <v>157.05400085449219</v>
       </c>
       <c r="J7">
         <v>146.0985000610352</v>
       </c>
       <c r="K7">
-        <v>133.5184004211426</v>
+        <v>133.51840042114259</v>
       </c>
       <c r="L7">
-        <v>91.96310007095337</v>
+        <v>91.963100070953374</v>
       </c>
       <c r="M7">
         <v>1.07</v>
@@ -1885,7 +1908,7 @@
         <v>12</v>
       </c>
       <c r="T7">
-        <v>22.22222222222222</v>
+        <v>22.222222222222221</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
@@ -1897,7 +1920,7 @@
         <v>1</v>
       </c>
       <c r="X7">
-        <v>35.41</v>
+        <v>35.409999999999997</v>
       </c>
       <c r="Y7">
         <v>168.67</v>
@@ -1909,13 +1932,13 @@
         <v>157</v>
       </c>
       <c r="AB7">
-        <v>32.27</v>
+        <v>32.270000000000003</v>
       </c>
       <c r="AC7">
         <v>320.5</v>
       </c>
       <c r="AD7">
-        <v>37.16</v>
+        <v>37.159999999999997</v>
       </c>
       <c r="AE7">
         <v>482.61</v>
@@ -1936,7 +1959,7 @@
         <v>213</v>
       </c>
       <c r="AK7">
-        <v>55.60507955220072</v>
+        <v>55.605079552200721</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1944,43 +1967,43 @@
         <v>43</v>
       </c>
       <c r="B8">
-        <v>93.16252274105518</v>
+        <v>93.162522741055184</v>
       </c>
       <c r="C8">
         <v>3160</v>
       </c>
       <c r="D8">
-        <v>77.34999999999999</v>
+        <v>77.349999999999994</v>
       </c>
       <c r="E8">
         <v>2.13</v>
       </c>
       <c r="F8">
-        <v>-0.7103237265009414</v>
+        <v>-0.71032372650094144</v>
       </c>
       <c r="G8">
         <v>2.13</v>
       </c>
       <c r="H8">
-        <v>-0.5941621724404541</v>
+        <v>-0.59416217244045411</v>
       </c>
       <c r="I8">
-        <v>78.26199798583984</v>
+        <v>78.261997985839841</v>
       </c>
       <c r="J8">
-        <v>74.47649917602538</v>
+        <v>74.476499176025385</v>
       </c>
       <c r="K8">
-        <v>69.13779960632324</v>
+        <v>69.137799606323242</v>
       </c>
       <c r="L8">
-        <v>58.54294986724854</v>
+        <v>58.542949867248538</v>
       </c>
       <c r="M8">
         <v>1.05</v>
       </c>
       <c r="N8">
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="P8">
         <v>0</v>
@@ -2028,7 +2051,7 @@
         <v>34.5</v>
       </c>
       <c r="AE8">
-        <v>269.03</v>
+        <v>269.02999999999997</v>
       </c>
       <c r="AF8">
         <v>-15.04</v>
@@ -2046,7 +2069,7 @@
         <v>214</v>
       </c>
       <c r="AK8">
-        <v>55.30051836374498</v>
+        <v>55.300518363744978</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -2054,7 +2077,7 @@
         <v>44</v>
       </c>
       <c r="B9">
-        <v>97.90782292298363</v>
+        <v>97.907822922983627</v>
       </c>
       <c r="C9">
         <v>2432</v>
@@ -2066,7 +2089,7 @@
         <v>7.55</v>
       </c>
       <c r="F9">
-        <v>1.866417539632789</v>
+        <v>1.8664175396327889</v>
       </c>
       <c r="G9">
         <v>5.04</v>
@@ -2075,16 +2098,16 @@
         <v>1.712479292743456</v>
       </c>
       <c r="I9">
-        <v>271.352001953125</v>
+        <v>271.35200195312501</v>
       </c>
       <c r="J9">
-        <v>299.2650009155274</v>
+        <v>299.26500091552742</v>
       </c>
       <c r="K9">
-        <v>269.228798828125</v>
+        <v>269.22879882812498</v>
       </c>
       <c r="L9">
-        <v>185.1860995864868</v>
+        <v>185.18609958648679</v>
       </c>
       <c r="M9">
         <v>0.91</v>
@@ -2105,7 +2128,7 @@
         <v>11</v>
       </c>
       <c r="T9">
-        <v>28.88888888888889</v>
+        <v>28.888888888888889</v>
       </c>
       <c r="U9" t="b">
         <v>0</v>
@@ -2144,7 +2167,7 @@
         <v>37.99</v>
       </c>
       <c r="AG9">
-        <v>38.12</v>
+        <v>38.119999999999997</v>
       </c>
       <c r="AH9" t="s">
         <v>165</v>
@@ -2156,7 +2179,7 @@
         <v>215</v>
       </c>
       <c r="AK9">
-        <v>52.04847439074508</v>
+        <v>52.048474390745078</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -2164,13 +2187,13 @@
         <v>45</v>
       </c>
       <c r="B10">
-        <v>91.82838083687082</v>
+        <v>91.828380836870821</v>
       </c>
       <c r="C10">
         <v>495</v>
       </c>
       <c r="D10">
-        <v>33.63</v>
+        <v>33.630000000000003</v>
       </c>
       <c r="E10">
         <v>3.2</v>
@@ -2182,25 +2205,25 @@
         <v>2.87</v>
       </c>
       <c r="H10">
-        <v>-0.007593552428050827</v>
+        <v>-7.5935524280508274E-3</v>
       </c>
       <c r="I10">
         <v>33.80800018310547</v>
       </c>
       <c r="J10">
-        <v>32.58649988174439</v>
+        <v>32.586499881744388</v>
       </c>
       <c r="K10">
         <v>30.16900005340576</v>
       </c>
       <c r="L10">
-        <v>23.63819997787476</v>
+        <v>23.638199977874759</v>
       </c>
       <c r="M10">
         <v>1.04</v>
       </c>
       <c r="N10">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -2274,7 +2297,7 @@
         <v>46</v>
       </c>
       <c r="B11">
-        <v>99.74226804123711</v>
+        <v>99.742268041237111</v>
       </c>
       <c r="C11">
         <v>394</v>
@@ -2292,22 +2315,22 @@
         <v>6.83</v>
       </c>
       <c r="H11">
-        <v>3.13134122493562</v>
+        <v>3.1313412249356198</v>
       </c>
       <c r="I11">
         <v>331.0519958496094</v>
       </c>
       <c r="J11">
-        <v>285.7799972534179</v>
+        <v>285.77999725341789</v>
       </c>
       <c r="K11">
         <v>202.1312989807129</v>
       </c>
       <c r="L11">
-        <v>109.5145497512817</v>
+        <v>109.51454975128171</v>
       </c>
       <c r="M11">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="N11">
         <v>1.64</v>
@@ -2325,7 +2348,7 @@
         <v>1</v>
       </c>
       <c r="T11">
-        <v>9.444444444444443</v>
+        <v>9.4444444444444429</v>
       </c>
       <c r="U11" t="b">
         <v>0</v>
@@ -2352,7 +2375,7 @@
         <v>313.01</v>
       </c>
       <c r="AC11">
-        <v>312.71</v>
+        <v>312.70999999999998</v>
       </c>
       <c r="AD11">
         <v>113.12</v>
@@ -2376,7 +2399,7 @@
         <v>210</v>
       </c>
       <c r="AK11">
-        <v>49.94498089767445</v>
+        <v>49.944980897674448</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -2384,7 +2407,7 @@
         <v>47</v>
       </c>
       <c r="B12">
-        <v>97.66525166767738</v>
+        <v>97.665251667677381</v>
       </c>
       <c r="C12">
         <v>589</v>
@@ -2402,7 +2425,7 @@
         <v>2.35</v>
       </c>
       <c r="H12">
-        <v>-0.4197769070313612</v>
+        <v>-0.41977690703136122</v>
       </c>
       <c r="I12">
         <v>114.1360000610352</v>
@@ -2411,16 +2434,16 @@
         <v>106.4370002746582</v>
       </c>
       <c r="K12">
-        <v>100.5531999206543</v>
+        <v>100.55319992065429</v>
       </c>
       <c r="L12">
-        <v>75.002050075531</v>
+        <v>75.002050075531002</v>
       </c>
       <c r="M12">
         <v>1.07</v>
       </c>
       <c r="N12">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -2435,7 +2458,7 @@
         <v>4</v>
       </c>
       <c r="T12">
-        <v>8.888888888888888</v>
+        <v>8.8888888888888875</v>
       </c>
       <c r="U12" t="b">
         <v>0</v>
@@ -2468,7 +2491,7 @@
         <v>1.36</v>
       </c>
       <c r="AE12">
-        <v>85.70999999999999</v>
+        <v>85.71</v>
       </c>
       <c r="AF12">
         <v>450</v>
@@ -2486,7 +2509,7 @@
         <v>216</v>
       </c>
       <c r="AK12">
-        <v>49.18925387823447</v>
+        <v>49.189253878234467</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -2494,7 +2517,7 @@
         <v>48</v>
       </c>
       <c r="B13">
-        <v>98.40812613705275</v>
+        <v>98.408126137052747</v>
       </c>
       <c r="C13">
         <v>1894</v>
@@ -2506,19 +2529,19 @@
         <v>3.92</v>
       </c>
       <c r="F13">
-        <v>0.1406664702480213</v>
+        <v>0.14066647024802131</v>
       </c>
       <c r="G13">
         <v>3.5</v>
       </c>
       <c r="H13">
-        <v>0.4917824348798058</v>
+        <v>0.49178243487980577</v>
       </c>
       <c r="I13">
         <v>212.8</v>
       </c>
       <c r="J13">
-        <v>205.9254997253418</v>
+        <v>205.92549972534181</v>
       </c>
       <c r="K13">
         <v>188.812799987793</v>
@@ -2530,7 +2553,7 @@
         <v>1.03</v>
       </c>
       <c r="N13">
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -2545,7 +2568,7 @@
         <v>3</v>
       </c>
       <c r="T13">
-        <v>6.111111111111111</v>
+        <v>6.1111111111111107</v>
       </c>
       <c r="U13" t="b">
         <v>0</v>
@@ -2569,7 +2592,7 @@
         <v>157</v>
       </c>
       <c r="AB13">
-        <v>607.3</v>
+        <v>607.29999999999995</v>
       </c>
       <c r="AC13">
         <v>342.23</v>
@@ -2596,7 +2619,7 @@
         <v>213</v>
       </c>
       <c r="AK13">
-        <v>49.15703088421498</v>
+        <v>49.157030884214983</v>
       </c>
     </row>
     <row r="14" spans="1:37">
@@ -2604,40 +2627,40 @@
         <v>49</v>
       </c>
       <c r="B14">
-        <v>98.77198302001213</v>
+        <v>98.771983020012129</v>
       </c>
       <c r="C14">
         <v>83</v>
       </c>
       <c r="D14">
-        <v>37.62</v>
+        <v>37.619999999999997</v>
       </c>
       <c r="E14">
         <v>5.15</v>
       </c>
       <c r="F14">
-        <v>0.725425097064348</v>
+        <v>0.72542509706434799</v>
       </c>
       <c r="G14">
         <v>4.34</v>
       </c>
       <c r="H14">
-        <v>1.157617084623615</v>
+        <v>1.1576170846236149</v>
       </c>
       <c r="I14">
-        <v>37.41599960327149</v>
+        <v>37.415999603271487</v>
       </c>
       <c r="J14">
-        <v>33.32150020599365</v>
+        <v>33.321500205993651</v>
       </c>
       <c r="K14">
-        <v>28.42959999084472</v>
+        <v>28.429599990844721</v>
       </c>
       <c r="L14">
-        <v>21.78077496051788</v>
+        <v>21.780774960517881</v>
       </c>
       <c r="M14">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="N14">
         <v>1.32</v>
@@ -2691,7 +2714,7 @@
         <v>-19.05</v>
       </c>
       <c r="AF14">
-        <v>16.67</v>
+        <v>16.670000000000002</v>
       </c>
       <c r="AG14">
         <v>800</v>
@@ -2706,7 +2729,7 @@
         <v>217</v>
       </c>
       <c r="AK14">
-        <v>48.90246322967881</v>
+        <v>48.902463229678808</v>
       </c>
     </row>
     <row r="15" spans="1:37">
@@ -2714,7 +2737,7 @@
         <v>50</v>
       </c>
       <c r="B15">
-        <v>95.45178896300789</v>
+        <v>95.451788963007886</v>
       </c>
       <c r="C15">
         <v>2921</v>
@@ -2726,13 +2749,13 @@
         <v>2.35</v>
       </c>
       <c r="F15">
-        <v>-0.6057327525988342</v>
+        <v>-0.60573275259883419</v>
       </c>
       <c r="G15">
         <v>1.92</v>
       </c>
       <c r="H15">
-        <v>-0.7606208348764064</v>
+        <v>-0.76062083487640642</v>
       </c>
       <c r="I15">
         <v>114.4860000610352</v>
@@ -2741,16 +2764,16 @@
         <v>111.1580001831055</v>
       </c>
       <c r="K15">
-        <v>98.5463998413086</v>
+        <v>98.546399841308599</v>
       </c>
       <c r="L15">
-        <v>80.21994997024537</v>
+        <v>80.219949970245366</v>
       </c>
       <c r="M15">
         <v>1.03</v>
       </c>
       <c r="N15">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="P15">
         <v>6</v>
@@ -2765,7 +2788,7 @@
         <v>0</v>
       </c>
       <c r="T15">
-        <v>4.444444444444444</v>
+        <v>4.4444444444444438</v>
       </c>
       <c r="U15" t="b">
         <v>0</v>
@@ -2786,13 +2809,13 @@
         <v>4.17</v>
       </c>
       <c r="AA15">
-        <v>-32.02</v>
+        <v>-32.020000000000003</v>
       </c>
       <c r="AB15">
         <v>834.72</v>
       </c>
       <c r="AC15">
-        <v>291.46</v>
+        <v>291.45999999999998</v>
       </c>
       <c r="AD15">
         <v>10.93</v>
@@ -2816,7 +2839,7 @@
         <v>218</v>
       </c>
       <c r="AK15">
-        <v>47.90274433075518</v>
+        <v>47.902744330755183</v>
       </c>
     </row>
     <row r="16" spans="1:37">
@@ -2836,25 +2859,25 @@
         <v>10.61</v>
       </c>
       <c r="F16">
-        <v>3.321182903907553</v>
+        <v>3.3211829039075531</v>
       </c>
       <c r="G16">
         <v>7.42</v>
       </c>
       <c r="H16">
-        <v>3.599010800350915</v>
+        <v>3.5990108003509151</v>
       </c>
       <c r="I16">
-        <v>31.08800048828125</v>
+        <v>31.088000488281249</v>
       </c>
       <c r="J16">
-        <v>25.27100019454956</v>
+        <v>25.271000194549561</v>
       </c>
       <c r="K16">
-        <v>22.01980007171631</v>
+        <v>22.019800071716311</v>
       </c>
       <c r="L16">
-        <v>17.95230001926422</v>
+        <v>17.952300019264221</v>
       </c>
       <c r="M16">
         <v>1.23</v>
@@ -2890,7 +2913,7 @@
         <v>8.09</v>
       </c>
       <c r="Y16">
-        <v>35.02</v>
+        <v>35.020000000000003</v>
       </c>
       <c r="Z16">
         <v>6.15</v>
@@ -2926,7 +2949,7 @@
         <v>219</v>
       </c>
       <c r="AK16">
-        <v>47.54283330999027</v>
+        <v>47.542833309990272</v>
       </c>
     </row>
     <row r="17" spans="1:37">
@@ -2934,7 +2957,7 @@
         <v>52</v>
       </c>
       <c r="B17">
-        <v>92.04063068526379</v>
+        <v>92.040630685263793</v>
       </c>
       <c r="C17">
         <v>1963</v>
@@ -2946,25 +2969,25 @@
         <v>3.59</v>
       </c>
       <c r="F17">
-        <v>-0.01621999060513943</v>
+        <v>-1.6219990605139432E-2</v>
       </c>
       <c r="G17">
         <v>2.56</v>
       </c>
       <c r="H17">
-        <v>-0.253318244595409</v>
+        <v>-0.25331824459540903</v>
       </c>
       <c r="I17">
-        <v>54.63400039672852</v>
+        <v>54.634000396728517</v>
       </c>
       <c r="J17">
-        <v>51.02600040435791</v>
+        <v>51.026000404357909</v>
       </c>
       <c r="K17">
-        <v>44.88559989929199</v>
+        <v>44.885599899291989</v>
       </c>
       <c r="L17">
-        <v>36.21359990119934</v>
+        <v>36.213599901199338</v>
       </c>
       <c r="M17">
         <v>1.07</v>
@@ -3024,7 +3047,7 @@
         <v>76.47</v>
       </c>
       <c r="AG17">
-        <v>-83.95999999999999</v>
+        <v>-83.96</v>
       </c>
       <c r="AH17" t="s">
         <v>163</v>
@@ -3036,7 +3059,7 @@
         <v>210</v>
       </c>
       <c r="AK17">
-        <v>47.11001699709058</v>
+        <v>47.110016997090582</v>
       </c>
     </row>
     <row r="18" spans="1:37">
@@ -3044,7 +3067,7 @@
         <v>53</v>
       </c>
       <c r="B18">
-        <v>93.7689508793208</v>
+        <v>93.768950879320798</v>
       </c>
       <c r="C18">
         <v>878</v>
@@ -3056,16 +3079,16 @@
         <v>2.33</v>
       </c>
       <c r="F18">
-        <v>-0.6152410229535712</v>
+        <v>-0.61524102295357119</v>
       </c>
       <c r="G18">
         <v>1.85</v>
       </c>
       <c r="H18">
-        <v>-0.8161070556883904</v>
+        <v>-0.81610705568839037</v>
       </c>
       <c r="I18">
-        <v>200.9399993896484</v>
+        <v>200.93999938964839</v>
       </c>
       <c r="J18">
         <v>195.3849990844727</v>
@@ -3074,13 +3097,13 @@
         <v>174.255400390625</v>
       </c>
       <c r="L18">
-        <v>136.0026504898071</v>
+        <v>136.00265048980711</v>
       </c>
       <c r="M18">
         <v>1.03</v>
       </c>
       <c r="N18">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="P18">
         <v>13</v>
@@ -3113,7 +3136,7 @@
         <v>209.87</v>
       </c>
       <c r="Z18">
-        <v>39.41</v>
+        <v>39.409999999999997</v>
       </c>
       <c r="AA18" t="s">
         <v>157</v>
@@ -3146,7 +3169,7 @@
         <v>220</v>
       </c>
       <c r="AK18">
-        <v>44.40337838506352</v>
+        <v>44.403378385063519</v>
       </c>
     </row>
     <row r="19" spans="1:37">
@@ -3154,7 +3177,7 @@
         <v>54</v>
       </c>
       <c r="B19">
-        <v>96.31594906003639</v>
+        <v>96.315949060036388</v>
       </c>
       <c r="C19">
         <v>2463</v>
@@ -3166,7 +3189,7 @@
         <v>3.77</v>
       </c>
       <c r="F19">
-        <v>0.06935444258749378</v>
+        <v>6.9354442587493778E-2</v>
       </c>
       <c r="G19">
         <v>3.01</v>
@@ -3175,16 +3198,16 @@
         <v>0.1033788891959171</v>
       </c>
       <c r="I19">
-        <v>58.70599899291992</v>
+        <v>58.705998992919923</v>
       </c>
       <c r="J19">
-        <v>55.55949993133545</v>
+        <v>55.559499931335452</v>
       </c>
       <c r="K19">
-        <v>48.67940017700195</v>
+        <v>48.679400177001952</v>
       </c>
       <c r="L19">
-        <v>41.09620010375976</v>
+        <v>41.096200103759763</v>
       </c>
       <c r="M19">
         <v>1.06</v>
@@ -3205,7 +3228,7 @@
         <v>0</v>
       </c>
       <c r="T19">
-        <v>0.5555555555555555</v>
+        <v>0.55555555555555547</v>
       </c>
       <c r="U19" t="b">
         <v>0</v>
@@ -3256,7 +3279,7 @@
         <v>221</v>
       </c>
       <c r="AK19">
-        <v>44.15655628423425</v>
+        <v>44.156556284234249</v>
       </c>
     </row>
     <row r="20" spans="1:37">
@@ -3264,7 +3287,7 @@
         <v>55</v>
       </c>
       <c r="B20">
-        <v>91.54032747119466</v>
+        <v>91.540327471194658</v>
       </c>
       <c r="C20">
         <v>2040</v>
@@ -3276,31 +3299,31 @@
         <v>3.9</v>
       </c>
       <c r="F20">
-        <v>0.1311581998932843</v>
+        <v>0.13115819989328431</v>
       </c>
       <c r="G20">
         <v>2.65</v>
       </c>
       <c r="H20">
-        <v>-0.1819788178371438</v>
+        <v>-0.18197881783714381</v>
       </c>
       <c r="I20">
-        <v>58.14400024414063</v>
+        <v>58.144000244140628</v>
       </c>
       <c r="J20">
-        <v>56.70449981689453</v>
+        <v>56.704499816894533</v>
       </c>
       <c r="K20">
-        <v>53.3207999420166</v>
+        <v>53.320799942016599</v>
       </c>
       <c r="L20">
-        <v>44.63359994888306</v>
+        <v>44.633599948883059</v>
       </c>
       <c r="M20">
         <v>1.03</v>
       </c>
       <c r="N20">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -3366,7 +3389,7 @@
         <v>217</v>
       </c>
       <c r="AK20">
-        <v>42.94935635891049</v>
+        <v>42.949356358910492</v>
       </c>
     </row>
     <row r="21" spans="1:37">
@@ -3374,7 +3397,7 @@
         <v>56</v>
       </c>
       <c r="B21">
-        <v>94.90600363856882</v>
+        <v>94.906003638568819</v>
       </c>
       <c r="C21">
         <v>1780</v>
@@ -3386,25 +3409,25 @@
         <v>3.45</v>
       </c>
       <c r="F21">
-        <v>-0.08277788308829838</v>
+        <v>-8.2777883088298379E-2</v>
       </c>
       <c r="G21">
         <v>2.87</v>
       </c>
       <c r="H21">
-        <v>-0.007593552428050827</v>
+        <v>-7.5935524280508274E-3</v>
       </c>
       <c r="I21">
-        <v>58.61999969482422</v>
+        <v>58.619999694824223</v>
       </c>
       <c r="J21">
-        <v>55.99150009155274</v>
+        <v>55.991500091552737</v>
       </c>
       <c r="K21">
-        <v>50.1983999633789</v>
+        <v>50.198399963378897</v>
       </c>
       <c r="L21">
-        <v>34.68309988021851</v>
+        <v>34.683099880218514</v>
       </c>
       <c r="M21">
         <v>1.05</v>
@@ -3425,7 +3448,7 @@
         <v>8</v>
       </c>
       <c r="T21">
-        <v>16.66666666666666</v>
+        <v>16.666666666666661</v>
       </c>
       <c r="U21" t="b">
         <v>0</v>
@@ -3476,7 +3499,7 @@
         <v>221</v>
       </c>
       <c r="AK21">
-        <v>42.94920513407433</v>
+        <v>42.949205134074333</v>
       </c>
     </row>
     <row r="22" spans="1:37">
@@ -3484,7 +3507,7 @@
         <v>57</v>
       </c>
       <c r="B22">
-        <v>94.54214675560945</v>
+        <v>94.542146755609451</v>
       </c>
       <c r="C22">
         <v>2238</v>
@@ -3493,25 +3516,25 @@
         <v>26.44</v>
       </c>
       <c r="E22">
-        <v>5.02</v>
+        <v>5.0199999999999996</v>
       </c>
       <c r="F22">
-        <v>0.663621339758557</v>
+        <v>0.66362133975855697</v>
       </c>
       <c r="G22">
         <v>3.38</v>
       </c>
       <c r="H22">
-        <v>0.3966631992021187</v>
+        <v>0.39666319920211868</v>
       </c>
       <c r="I22">
-        <v>26.04800071716308</v>
+        <v>26.048000717163081</v>
       </c>
       <c r="J22">
-        <v>21.5705002784729</v>
+        <v>21.570500278472899</v>
       </c>
       <c r="K22">
-        <v>18.30800003051758</v>
+        <v>18.308000030517579</v>
       </c>
       <c r="L22">
         <v>16.45809999465942</v>
@@ -3565,7 +3588,7 @@
         <v>248.36</v>
       </c>
       <c r="AD22">
-        <v>16.1</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="AE22">
         <v>288.89</v>
@@ -3586,7 +3609,7 @@
         <v>222</v>
       </c>
       <c r="AK22">
-        <v>42.68796068581066</v>
+        <v>42.687960685810658</v>
       </c>
     </row>
     <row r="23" spans="1:37">
@@ -3594,7 +3617,7 @@
         <v>58</v>
       </c>
       <c r="B23">
-        <v>97.1497877501516</v>
+        <v>97.149787750151603</v>
       </c>
       <c r="C23">
         <v>283</v>
@@ -3606,16 +3629,16 @@
         <v>4.41</v>
       </c>
       <c r="F23">
-        <v>0.3736190939390783</v>
+        <v>0.37361909393907827</v>
       </c>
       <c r="G23">
         <v>3.31</v>
       </c>
       <c r="H23">
-        <v>0.3411769783901348</v>
+        <v>0.34117697839013478</v>
       </c>
       <c r="I23">
-        <v>129.0720016479492</v>
+        <v>129.07200164794921</v>
       </c>
       <c r="J23">
         <v>126.6270000457764</v>
@@ -3630,7 +3653,7 @@
         <v>1.02</v>
       </c>
       <c r="N23">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -3645,7 +3668,7 @@
         <v>2</v>
       </c>
       <c r="T23">
-        <v>11.11111111111111</v>
+        <v>11.111111111111111</v>
       </c>
       <c r="U23" t="b">
         <v>0</v>
@@ -3660,13 +3683,13 @@
         <v>43.27</v>
       </c>
       <c r="Y23">
-        <v>145.67</v>
+        <v>145.66999999999999</v>
       </c>
       <c r="Z23">
         <v>44.57</v>
       </c>
       <c r="AA23">
-        <v>82.84999999999999</v>
+        <v>82.85</v>
       </c>
       <c r="AB23">
         <v>51.01</v>
@@ -3696,7 +3719,7 @@
         <v>215</v>
       </c>
       <c r="AK23">
-        <v>39.62402790718478</v>
+        <v>39.624027907184782</v>
       </c>
     </row>
     <row r="24" spans="1:37">
@@ -3704,43 +3727,43 @@
         <v>59</v>
       </c>
       <c r="B24">
-        <v>90.93389933292904</v>
+        <v>90.933899332929045</v>
       </c>
       <c r="C24">
         <v>1809</v>
       </c>
       <c r="D24">
-        <v>83.90000000000001</v>
+        <v>83.9</v>
       </c>
       <c r="E24">
         <v>2.37</v>
       </c>
       <c r="F24">
-        <v>-0.5962244822440972</v>
+        <v>-0.59622448224409719</v>
       </c>
       <c r="G24">
         <v>1.64</v>
       </c>
       <c r="H24">
-        <v>-0.9825657181243427</v>
+        <v>-0.98256571812434268</v>
       </c>
       <c r="I24">
-        <v>84.76399993896484</v>
+        <v>84.763999938964844</v>
       </c>
       <c r="J24">
-        <v>82.40999984741211</v>
+        <v>82.409999847412109</v>
       </c>
       <c r="K24">
         <v>76.2331999206543</v>
       </c>
       <c r="L24">
-        <v>66.14554990768433</v>
+        <v>66.145549907684327</v>
       </c>
       <c r="M24">
         <v>1.03</v>
       </c>
       <c r="N24">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="P24">
         <v>0</v>
@@ -3782,10 +3805,10 @@
         <v>28.38</v>
       </c>
       <c r="AC24">
-        <v>4214.94</v>
+        <v>4214.9399999999996</v>
       </c>
       <c r="AD24">
-        <v>2.22</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="AE24">
         <v>65.22</v>
@@ -3806,7 +3829,7 @@
         <v>223</v>
       </c>
       <c r="AK24">
-        <v>39.58700077792406</v>
+        <v>39.587000777924061</v>
       </c>
     </row>
     <row r="25" spans="1:37">
@@ -3814,7 +3837,7 @@
         <v>60</v>
       </c>
       <c r="B25">
-        <v>97.05882352941177</v>
+        <v>97.058823529411768</v>
       </c>
       <c r="C25">
         <v>1700</v>
@@ -3826,25 +3849,25 @@
         <v>5.16</v>
       </c>
       <c r="F25">
-        <v>0.7301792322417163</v>
+        <v>0.73017923224171633</v>
       </c>
       <c r="G25">
         <v>3.92</v>
       </c>
       <c r="H25">
-        <v>0.8246997597517103</v>
+        <v>0.82469975975171028</v>
       </c>
       <c r="I25">
-        <v>23.12600021362305</v>
+        <v>23.126000213623051</v>
       </c>
       <c r="J25">
         <v>22.07800016403198</v>
       </c>
       <c r="K25">
-        <v>18.83999994277954</v>
+        <v>18.839999942779539</v>
       </c>
       <c r="L25">
-        <v>16.13449995040894</v>
+        <v>16.134499950408941</v>
       </c>
       <c r="M25">
         <v>1.05</v>
@@ -3886,7 +3909,7 @@
         <v>1.76</v>
       </c>
       <c r="AA25">
-        <v>9.199999999999999</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="AB25">
         <v>423.23</v>
@@ -3916,7 +3939,7 @@
         <v>224</v>
       </c>
       <c r="AK25">
-        <v>38.52837167996648</v>
+        <v>38.528371679966483</v>
       </c>
     </row>
     <row r="26" spans="1:37">
@@ -3936,28 +3959,28 @@
         <v>6.3</v>
       </c>
       <c r="F26">
-        <v>1.272150642461726</v>
+        <v>1.2721506424617259</v>
       </c>
       <c r="G26">
         <v>4.41</v>
       </c>
       <c r="H26">
-        <v>1.213103305435599</v>
+        <v>1.2131033054355991</v>
       </c>
       <c r="I26">
-        <v>65.98200073242188</v>
+        <v>65.982000732421881</v>
       </c>
       <c r="J26">
-        <v>60.50299987792969</v>
+        <v>60.502999877929689</v>
       </c>
       <c r="K26">
         <v>48.86640007019043</v>
       </c>
       <c r="L26">
-        <v>31.55029996871948</v>
+        <v>31.550299968719479</v>
       </c>
       <c r="M26">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="N26">
         <v>1.35</v>
@@ -4026,7 +4049,7 @@
         <v>225</v>
       </c>
       <c r="AK26">
-        <v>38.42588836944547</v>
+        <v>38.425888369445467</v>
       </c>
     </row>
     <row r="27" spans="1:37">
@@ -4034,7 +4057,7 @@
         <v>62</v>
       </c>
       <c r="B27">
-        <v>94.28441479684658</v>
+        <v>94.284414796846576</v>
       </c>
       <c r="C27">
         <v>1286</v>
@@ -4046,31 +4069,31 @@
         <v>2.77</v>
       </c>
       <c r="F27">
-        <v>-0.406059075149357</v>
+        <v>-0.40605907514935702</v>
       </c>
       <c r="G27">
         <v>1.84</v>
       </c>
       <c r="H27">
-        <v>-0.8240336586615309</v>
+        <v>-0.82403365866153089</v>
       </c>
       <c r="I27">
-        <v>79.04400024414062</v>
+        <v>79.044000244140619</v>
       </c>
       <c r="J27">
-        <v>74.36050033569336</v>
+        <v>74.360500335693359</v>
       </c>
       <c r="K27">
         <v>68.04980003356934</v>
       </c>
       <c r="L27">
-        <v>53.70515001296997</v>
+        <v>53.705150012969973</v>
       </c>
       <c r="M27">
         <v>1.06</v>
       </c>
       <c r="N27">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -4103,7 +4126,7 @@
         <v>80.53</v>
       </c>
       <c r="Z27">
-        <v>16.15</v>
+        <v>16.149999999999999</v>
       </c>
       <c r="AA27">
         <v>-1.01</v>
@@ -4124,7 +4147,7 @@
         <v>-2.94</v>
       </c>
       <c r="AG27">
-        <v>134.48</v>
+        <v>134.47999999999999</v>
       </c>
       <c r="AH27" t="s">
         <v>175</v>
@@ -4136,7 +4159,7 @@
         <v>217</v>
       </c>
       <c r="AK27">
-        <v>37.45537170984728</v>
+        <v>37.455371709847277</v>
       </c>
     </row>
     <row r="28" spans="1:37">
@@ -4144,7 +4167,7 @@
         <v>63</v>
       </c>
       <c r="B28">
-        <v>92.93511218920558</v>
+        <v>92.935112189205583</v>
       </c>
       <c r="C28">
         <v>604</v>
@@ -4156,25 +4179,25 @@
         <v>4.95</v>
       </c>
       <c r="F28">
-        <v>0.6303423935169777</v>
+        <v>0.63034239351697774</v>
       </c>
       <c r="G28">
         <v>2.96</v>
       </c>
       <c r="H28">
-        <v>0.06374587433021431</v>
+        <v>6.3745874330214308E-2</v>
       </c>
       <c r="I28">
-        <v>10.87999992370606</v>
+        <v>10.879999923706061</v>
       </c>
       <c r="J28">
         <v>10.55400009155273</v>
       </c>
       <c r="K28">
-        <v>9.0314000415802</v>
+        <v>9.0314000415802003</v>
       </c>
       <c r="L28">
-        <v>6.509300000667572</v>
+        <v>6.5093000006675723</v>
       </c>
       <c r="M28">
         <v>1.03</v>
@@ -4246,7 +4269,7 @@
         <v>225</v>
       </c>
       <c r="AK28">
-        <v>37.14897980555448</v>
+        <v>37.148979805554482</v>
       </c>
     </row>
     <row r="29" spans="1:37">
@@ -4266,19 +4289,19 @@
         <v>3.22</v>
       </c>
       <c r="F29">
-        <v>-0.192122992167774</v>
+        <v>-0.19212299216777401</v>
       </c>
       <c r="G29">
         <v>2.23</v>
       </c>
       <c r="H29">
-        <v>-0.5148961427090483</v>
+        <v>-0.51489614270904827</v>
       </c>
       <c r="I29">
         <v>154.2279998779297</v>
       </c>
       <c r="J29">
-        <v>153.8757507324219</v>
+        <v>153.87575073242189</v>
       </c>
       <c r="K29">
         <v>143.9952996826172</v>
@@ -4356,7 +4379,7 @@
         <v>226</v>
       </c>
       <c r="AK29">
-        <v>37.04434094618669</v>
+        <v>37.044340946186693</v>
       </c>
     </row>
     <row r="30" spans="1:37">
@@ -4364,7 +4387,7 @@
         <v>65</v>
       </c>
       <c r="B30">
-        <v>94.0721649484536</v>
+        <v>94.072164948453604</v>
       </c>
       <c r="C30">
         <v>26</v>
@@ -4376,7 +4399,7 @@
         <v>3.31</v>
       </c>
       <c r="F30">
-        <v>-0.1493357755714576</v>
+        <v>-0.14933577557145761</v>
       </c>
       <c r="G30">
         <v>3.18</v>
@@ -4388,16 +4411,16 @@
         <v>15.92600002288818</v>
       </c>
       <c r="J30">
-        <v>14.03850002288818</v>
+        <v>14.038500022888179</v>
       </c>
       <c r="K30">
         <v>11.22180004119873</v>
       </c>
       <c r="L30">
-        <v>8.248624989986419</v>
+        <v>8.2486249899864195</v>
       </c>
       <c r="M30">
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="N30">
         <v>1.42</v>
@@ -4415,7 +4438,7 @@
         <v>2</v>
       </c>
       <c r="T30">
-        <v>4.444444444444444</v>
+        <v>4.4444444444444438</v>
       </c>
       <c r="U30" t="b">
         <v>0</v>
@@ -4466,7 +4489,7 @@
         <v>227</v>
       </c>
       <c r="AK30">
-        <v>36.88622962836418</v>
+        <v>36.886229628364177</v>
       </c>
     </row>
     <row r="31" spans="1:37">
@@ -4474,7 +4497,7 @@
         <v>66</v>
       </c>
       <c r="B31">
-        <v>97.42268041237114</v>
+        <v>97.422680412371136</v>
       </c>
       <c r="C31">
         <v>3320</v>
@@ -4486,19 +4509,19 @@
         <v>5.62</v>
       </c>
       <c r="F31">
-        <v>0.9488694504006676</v>
+        <v>0.94886945040066761</v>
       </c>
       <c r="G31">
         <v>3.71</v>
       </c>
       <c r="H31">
-        <v>0.6582410973157581</v>
+        <v>0.65824109731575808</v>
       </c>
       <c r="I31">
-        <v>18.75999946594238</v>
+        <v>18.759999465942379</v>
       </c>
       <c r="J31">
-        <v>16.17949962615967</v>
+        <v>16.179499626159672</v>
       </c>
       <c r="K31">
         <v>13.27539987564087</v>
@@ -4507,7 +4530,7 @@
         <v>10.73032495975494</v>
       </c>
       <c r="M31">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="N31">
         <v>1.41</v>
@@ -4552,7 +4575,7 @@
         <v>172.46</v>
       </c>
       <c r="AC31">
-        <v>320.47</v>
+        <v>320.47000000000003</v>
       </c>
       <c r="AD31">
         <v>2</v>
@@ -4576,7 +4599,7 @@
         <v>210</v>
       </c>
       <c r="AK31">
-        <v>36.71669181918364</v>
+        <v>36.716691819183637</v>
       </c>
     </row>
     <row r="32" spans="1:37">
@@ -4590,37 +4613,37 @@
         <v>1726</v>
       </c>
       <c r="D32">
-        <v>142.05</v>
+        <v>142.05000000000001</v>
       </c>
       <c r="E32">
         <v>2</v>
       </c>
       <c r="F32">
-        <v>-0.772127483806732</v>
+        <v>-0.77212748380673202</v>
       </c>
       <c r="G32">
         <v>2.02</v>
       </c>
       <c r="H32">
-        <v>-0.6813548051450005</v>
+        <v>-0.68135480514500046</v>
       </c>
       <c r="I32">
-        <v>144.3340026855469</v>
+        <v>144.33400268554689</v>
       </c>
       <c r="J32">
         <v>141.0319999694824</v>
       </c>
       <c r="K32">
-        <v>131.4903996276855</v>
+        <v>131.49039962768549</v>
       </c>
       <c r="L32">
-        <v>108.0369999694824</v>
+        <v>108.03699996948239</v>
       </c>
       <c r="M32">
         <v>1.02</v>
       </c>
       <c r="N32">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="P32">
         <v>0</v>
@@ -4659,7 +4682,7 @@
         <v>157</v>
       </c>
       <c r="AB32">
-        <v>86.70999999999999</v>
+        <v>86.71</v>
       </c>
       <c r="AC32">
         <v>562.4</v>
@@ -4686,7 +4709,7 @@
         <v>228</v>
       </c>
       <c r="AK32">
-        <v>36.13678544661703</v>
+        <v>36.136785446617033</v>
       </c>
     </row>
     <row r="33" spans="1:37">
@@ -4694,7 +4717,7 @@
         <v>68</v>
       </c>
       <c r="B33">
-        <v>95.92177077016373</v>
+        <v>95.921770770163732</v>
       </c>
       <c r="C33">
         <v>2891</v>
@@ -4706,7 +4729,7 @@
         <v>2.69</v>
       </c>
       <c r="F33">
-        <v>-0.444092156568305</v>
+        <v>-0.44409215656830497</v>
       </c>
       <c r="G33">
         <v>2.58</v>
@@ -4715,22 +4738,22 @@
         <v>-0.2374650386491278</v>
       </c>
       <c r="I33">
-        <v>493.7299926757813</v>
+        <v>493.72999267578132</v>
       </c>
       <c r="J33">
-        <v>462.7864974975586</v>
+        <v>462.78649749755863</v>
       </c>
       <c r="K33">
-        <v>426.1779998779297</v>
+        <v>426.17799987792972</v>
       </c>
       <c r="L33">
-        <v>343.7913497161865</v>
+        <v>343.79134971618652</v>
       </c>
       <c r="M33">
         <v>1.07</v>
       </c>
       <c r="N33">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="P33">
         <v>1</v>
@@ -4772,7 +4795,7 @@
         <v>63.79</v>
       </c>
       <c r="AC33">
-        <v>39.73</v>
+        <v>39.729999999999997</v>
       </c>
       <c r="AD33">
         <v>33.5</v>
@@ -4796,7 +4819,7 @@
         <v>228</v>
       </c>
       <c r="AK33">
-        <v>36.09494867853897</v>
+        <v>36.094948678538969</v>
       </c>
     </row>
     <row r="34" spans="1:37">
@@ -4804,7 +4827,7 @@
         <v>69</v>
       </c>
       <c r="B34">
-        <v>97.63493026076409</v>
+        <v>97.634930260764094</v>
       </c>
       <c r="C34">
         <v>1928</v>
@@ -4816,25 +4839,25 @@
         <v>3.64</v>
       </c>
       <c r="F34">
-        <v>0.007550685281703234</v>
+        <v>7.5506852817032342E-3</v>
       </c>
       <c r="G34">
         <v>3.35</v>
       </c>
       <c r="H34">
-        <v>0.3728833902826972</v>
+        <v>0.37288339028269718</v>
       </c>
       <c r="I34">
-        <v>16.74199981689453</v>
+        <v>16.741999816894531</v>
       </c>
       <c r="J34">
         <v>16.15949997901917</v>
       </c>
       <c r="K34">
-        <v>13.55759998321533</v>
+        <v>13.557599983215329</v>
       </c>
       <c r="L34">
-        <v>10.33825000524521</v>
+        <v>10.338250005245211</v>
       </c>
       <c r="M34">
         <v>1.04</v>
@@ -4870,13 +4893,13 @@
         <v>4.63</v>
       </c>
       <c r="Y34">
-        <v>18.24</v>
+        <v>18.239999999999998</v>
       </c>
       <c r="Z34">
         <v>4.54</v>
       </c>
       <c r="AA34">
-        <v>36.12</v>
+        <v>36.119999999999997</v>
       </c>
       <c r="AB34">
         <v>111.4</v>
@@ -4885,7 +4908,7 @@
         <v>244.88</v>
       </c>
       <c r="AD34">
-        <v>20.06</v>
+        <v>20.059999999999999</v>
       </c>
       <c r="AE34">
         <v>-34.54</v>
@@ -4906,7 +4929,7 @@
         <v>229</v>
       </c>
       <c r="AK34">
-        <v>35.81013326393158</v>
+        <v>35.810133263931583</v>
       </c>
     </row>
     <row r="35" spans="1:37">
@@ -4938,13 +4961,13 @@
         <v>195.9</v>
       </c>
       <c r="J35">
-        <v>186.4469985961914</v>
+        <v>186.44699859619141</v>
       </c>
       <c r="K35">
-        <v>166.2803994750977</v>
+        <v>166.28039947509771</v>
       </c>
       <c r="L35">
-        <v>126.3068499755859</v>
+        <v>126.30684997558591</v>
       </c>
       <c r="M35">
         <v>1.05</v>
@@ -4965,7 +4988,7 @@
         <v>3</v>
       </c>
       <c r="T35">
-        <v>10.55555555555556</v>
+        <v>10.555555555555561</v>
       </c>
       <c r="U35" t="b">
         <v>0</v>
@@ -5016,7 +5039,7 @@
         <v>228</v>
       </c>
       <c r="AK35">
-        <v>35.46542778845953</v>
+        <v>35.465427788459529</v>
       </c>
     </row>
     <row r="36" spans="1:37">
@@ -5024,7 +5047,7 @@
         <v>71</v>
       </c>
       <c r="B36">
-        <v>92.55609460278957</v>
+        <v>92.556094602789571</v>
       </c>
       <c r="C36">
         <v>1722</v>
@@ -5036,19 +5059,19 @@
         <v>2.09</v>
       </c>
       <c r="F36">
-        <v>-0.7293402672104156</v>
+        <v>-0.72934026721041556</v>
       </c>
       <c r="G36">
         <v>2.37</v>
       </c>
       <c r="H36">
-        <v>-0.40392370108508</v>
+        <v>-0.40392370108508002</v>
       </c>
       <c r="I36">
-        <v>50.90600051879883</v>
+        <v>50.906000518798827</v>
       </c>
       <c r="J36">
-        <v>51.97900009155273</v>
+        <v>51.979000091552727</v>
       </c>
       <c r="K36">
         <v>48.17699989318848</v>
@@ -5111,7 +5134,7 @@
         <v>7.25</v>
       </c>
       <c r="AF36">
-        <v>86.48999999999999</v>
+        <v>86.49</v>
       </c>
       <c r="AG36">
         <v>29.82</v>
@@ -5126,7 +5149,7 @@
         <v>226</v>
       </c>
       <c r="AK36">
-        <v>35.19334078663891</v>
+        <v>35.193340786638913</v>
       </c>
     </row>
     <row r="37" spans="1:37">
@@ -5134,7 +5157,7 @@
         <v>72</v>
       </c>
       <c r="B37">
-        <v>97.68041237113401</v>
+        <v>97.680412371134011</v>
       </c>
       <c r="C37">
         <v>4445</v>
@@ -5146,7 +5169,7 @@
         <v>5.22</v>
       </c>
       <c r="F37">
-        <v>0.7587040433059272</v>
+        <v>0.75870404330592722</v>
       </c>
       <c r="G37">
         <v>3.16</v>
@@ -5155,13 +5178,13 @@
         <v>0.2222779337930261</v>
       </c>
       <c r="I37">
-        <v>353.9800048828125</v>
+        <v>353.98000488281252</v>
       </c>
       <c r="J37">
-        <v>327.6285034179688</v>
+        <v>327.62850341796877</v>
       </c>
       <c r="K37">
-        <v>275.1208016967773</v>
+        <v>275.12080169677728</v>
       </c>
       <c r="L37">
         <v>177.9040006637573</v>
@@ -5185,7 +5208,7 @@
         <v>0</v>
       </c>
       <c r="T37">
-        <v>8.888888888888888</v>
+        <v>8.8888888888888875</v>
       </c>
       <c r="U37" t="b">
         <v>0</v>
@@ -5215,7 +5238,7 @@
         <v>45.75</v>
       </c>
       <c r="AD37">
-        <v>623.9400000000001</v>
+        <v>623.94000000000005</v>
       </c>
       <c r="AE37">
         <v>23.26</v>
@@ -5236,7 +5259,7 @@
         <v>230</v>
       </c>
       <c r="AK37">
-        <v>34.43811295979135</v>
+        <v>34.438112959791347</v>
       </c>
     </row>
     <row r="38" spans="1:37">
@@ -5244,7 +5267,7 @@
         <v>73</v>
       </c>
       <c r="B38">
-        <v>93.96604002425713</v>
+        <v>93.966040024257126</v>
       </c>
       <c r="C38">
         <v>1276</v>
@@ -5256,25 +5279,25 @@
         <v>2.88</v>
       </c>
       <c r="F38">
-        <v>-0.3537635881983034</v>
+        <v>-0.35376358819830339</v>
       </c>
       <c r="G38">
         <v>2.41</v>
       </c>
       <c r="H38">
-        <v>-0.3722172891925176</v>
+        <v>-0.37221728919251762</v>
       </c>
       <c r="I38">
-        <v>38.66800003051758</v>
+        <v>38.668000030517582</v>
       </c>
       <c r="J38">
-        <v>37.65500030517578</v>
+        <v>37.655000305175783</v>
       </c>
       <c r="K38">
-        <v>35.72160003662109</v>
+        <v>35.721600036621091</v>
       </c>
       <c r="L38">
-        <v>29.71700000762939</v>
+        <v>29.717000007629391</v>
       </c>
       <c r="M38">
         <v>1.03</v>
@@ -5310,7 +5333,7 @@
         <v>16.88</v>
       </c>
       <c r="Y38">
-        <v>40.34</v>
+        <v>40.340000000000003</v>
       </c>
       <c r="Z38">
         <v>6.72</v>
@@ -5328,7 +5351,7 @@
         <v>17.52</v>
       </c>
       <c r="AE38">
-        <v>79.90000000000001</v>
+        <v>79.900000000000006</v>
       </c>
       <c r="AF38">
         <v>246.26</v>
@@ -5354,7 +5377,7 @@
         <v>74</v>
       </c>
       <c r="B39">
-        <v>91.43420254699818</v>
+        <v>91.434202546998179</v>
       </c>
       <c r="C39">
         <v>579</v>
@@ -5366,13 +5389,13 @@
         <v>1.48</v>
       </c>
       <c r="F39">
-        <v>-1.019342513029894</v>
+        <v>-1.0193425130298941</v>
       </c>
       <c r="G39">
         <v>1.96</v>
       </c>
       <c r="H39">
-        <v>-0.728914422983844</v>
+        <v>-0.72891442298384401</v>
       </c>
       <c r="I39">
         <v>880.0160034179687</v>
@@ -5381,16 +5404,16 @@
         <v>840.2704956054688</v>
       </c>
       <c r="K39">
-        <v>773.446796875</v>
+        <v>773.44679687500002</v>
       </c>
       <c r="L39">
-        <v>670.5841998291015</v>
+        <v>670.58419982910152</v>
       </c>
       <c r="M39">
         <v>1.05</v>
       </c>
       <c r="N39">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="O39" t="s">
         <v>156</v>
@@ -5408,7 +5431,7 @@
         <v>0</v>
       </c>
       <c r="T39">
-        <v>7.222222222222221</v>
+        <v>7.2222222222222214</v>
       </c>
       <c r="U39" t="b">
         <v>0</v>
@@ -5432,7 +5455,7 @@
         <v>35.03</v>
       </c>
       <c r="AB39">
-        <v>64.59999999999999</v>
+        <v>64.599999999999994</v>
       </c>
       <c r="AC39">
         <v>44.8</v>
@@ -5459,7 +5482,7 @@
         <v>232</v>
       </c>
       <c r="AK39">
-        <v>33.40247346738459</v>
+        <v>33.402473467384588</v>
       </c>
     </row>
     <row r="40" spans="1:37">
@@ -5467,19 +5490,19 @@
         <v>75</v>
       </c>
       <c r="B40">
-        <v>99.87871437234688</v>
+        <v>99.878714372346877</v>
       </c>
       <c r="C40">
         <v>2089</v>
       </c>
       <c r="D40">
-        <v>93.01000000000001</v>
+        <v>93.01</v>
       </c>
       <c r="E40">
         <v>11.8</v>
       </c>
       <c r="F40">
-        <v>3.886924990014406</v>
+        <v>3.8869249900144061</v>
       </c>
       <c r="G40">
         <v>7.81</v>
@@ -5488,16 +5511,16 @@
         <v>3.908148316303397</v>
       </c>
       <c r="I40">
-        <v>91.16600036621094</v>
+        <v>91.166000366210938</v>
       </c>
       <c r="J40">
-        <v>72.81699962615967</v>
+        <v>72.816999626159671</v>
       </c>
       <c r="K40">
-        <v>54.07220001220703</v>
+        <v>54.072200012207027</v>
       </c>
       <c r="L40">
-        <v>41.23660004615784</v>
+        <v>41.236600046157839</v>
       </c>
       <c r="M40">
         <v>1.25</v>
@@ -5548,13 +5571,13 @@
         <v>103.31</v>
       </c>
       <c r="AD40">
-        <v>35.12</v>
+        <v>35.119999999999997</v>
       </c>
       <c r="AE40">
         <v>-92.16</v>
       </c>
       <c r="AF40">
-        <v>-81.79000000000001</v>
+        <v>-81.790000000000006</v>
       </c>
       <c r="AG40">
         <v>9233.33</v>
@@ -5569,7 +5592,7 @@
         <v>210</v>
       </c>
       <c r="AK40">
-        <v>33.37549548511249</v>
+        <v>33.375495485112488</v>
       </c>
     </row>
     <row r="41" spans="1:37">
@@ -5577,7 +5600,7 @@
         <v>76</v>
       </c>
       <c r="B41">
-        <v>98.68101879927229</v>
+        <v>98.681018799272294</v>
       </c>
       <c r="C41">
         <v>843</v>
@@ -5589,25 +5612,25 @@
         <v>2.59</v>
       </c>
       <c r="F41">
-        <v>-0.4916335083419902</v>
+        <v>-0.49163350834199021</v>
       </c>
       <c r="G41">
         <v>1.99</v>
       </c>
       <c r="H41">
-        <v>-0.7051346140644222</v>
+        <v>-0.70513461406442224</v>
       </c>
       <c r="I41">
         <v>141.8019989013672</v>
       </c>
       <c r="J41">
-        <v>141.4530006408691</v>
+        <v>141.45300064086911</v>
       </c>
       <c r="K41">
-        <v>135.3736004638672</v>
+        <v>135.37360046386721</v>
       </c>
       <c r="L41">
-        <v>95.73560007095337</v>
+        <v>95.735600070953367</v>
       </c>
       <c r="M41">
         <v>1</v>
@@ -5667,7 +5690,7 @@
         <v>41.67</v>
       </c>
       <c r="AG41">
-        <v>-90.23999999999999</v>
+        <v>-90.24</v>
       </c>
       <c r="AH41" t="s">
         <v>169</v>
@@ -5679,7 +5702,7 @@
         <v>233</v>
       </c>
       <c r="AK41">
-        <v>32.92450550329313</v>
+        <v>32.924505503293133</v>
       </c>
     </row>
     <row r="42" spans="1:37">
@@ -5687,7 +5710,7 @@
         <v>77</v>
       </c>
       <c r="B42">
-        <v>94.32989690721649</v>
+        <v>94.329896907216494</v>
       </c>
       <c r="C42">
         <v>4273</v>
@@ -5699,22 +5722,22 @@
         <v>4.58</v>
       </c>
       <c r="F42">
-        <v>0.4544393919543429</v>
+        <v>0.45443939195434291</v>
       </c>
       <c r="G42">
         <v>2.9</v>
       </c>
       <c r="H42">
-        <v>0.01618625649137077</v>
+        <v>1.618625649137077E-2</v>
       </c>
       <c r="I42">
-        <v>343.9019958496094</v>
+        <v>343.90199584960942</v>
       </c>
       <c r="J42">
-        <v>334.0190002441406</v>
+        <v>334.01900024414061</v>
       </c>
       <c r="K42">
-        <v>306.9626013183594</v>
+        <v>306.96260131835942</v>
       </c>
       <c r="L42">
         <v>244.1663005065918</v>
@@ -5723,7 +5746,7 @@
         <v>1.03</v>
       </c>
       <c r="N42">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="P42">
         <v>0</v>
@@ -5756,7 +5779,7 @@
         <v>351.8</v>
       </c>
       <c r="Z42">
-        <v>4.81</v>
+        <v>4.8099999999999996</v>
       </c>
       <c r="AA42">
         <v>5.92</v>
@@ -5789,7 +5812,7 @@
         <v>217</v>
       </c>
       <c r="AK42">
-        <v>32.73643639903651</v>
+        <v>32.736436399036513</v>
       </c>
     </row>
     <row r="43" spans="1:37">
@@ -5797,13 +5820,13 @@
         <v>78</v>
       </c>
       <c r="B43">
-        <v>97.72589448150394</v>
+        <v>97.725894481503943</v>
       </c>
       <c r="C43">
         <v>824</v>
       </c>
       <c r="D43">
-        <v>84.95999999999999</v>
+        <v>84.96</v>
       </c>
       <c r="E43">
         <v>3.2</v>
@@ -5815,19 +5838,19 @@
         <v>3.47</v>
       </c>
       <c r="H43">
-        <v>0.4680026259603842</v>
+        <v>0.46800262596038422</v>
       </c>
       <c r="I43">
-        <v>85.12599945068359</v>
+        <v>85.125999450683594</v>
       </c>
       <c r="J43">
-        <v>83.87650032043457</v>
+        <v>83.876500320434573</v>
       </c>
       <c r="K43">
-        <v>68.69420036315918</v>
+        <v>68.694200363159183</v>
       </c>
       <c r="L43">
-        <v>54.44610000610351</v>
+        <v>54.446100006103507</v>
       </c>
       <c r="M43">
         <v>1.01</v>
@@ -5848,7 +5871,7 @@
         <v>4</v>
       </c>
       <c r="T43">
-        <v>10.55555555555556</v>
+        <v>10.555555555555561</v>
       </c>
       <c r="U43" t="b">
         <v>0</v>
@@ -5863,7 +5886,7 @@
         <v>25.84</v>
       </c>
       <c r="Y43">
-        <v>93.15000000000001</v>
+        <v>93.15</v>
       </c>
       <c r="Z43">
         <v>11.37</v>
@@ -5899,7 +5922,7 @@
         <v>234</v>
       </c>
       <c r="AK43">
-        <v>32.71758875385839</v>
+        <v>32.717588753858386</v>
       </c>
     </row>
     <row r="44" spans="1:37">
@@ -5907,7 +5930,7 @@
         <v>79</v>
       </c>
       <c r="B44">
-        <v>96.57368101879928</v>
+        <v>96.573681018799277</v>
       </c>
       <c r="C44">
         <v>232</v>
@@ -5919,28 +5942,28 @@
         <v>8.4</v>
       </c>
       <c r="F44">
-        <v>2.270519029709113</v>
+        <v>2.2705190297091131</v>
       </c>
       <c r="G44">
         <v>6.56</v>
       </c>
       <c r="H44">
-        <v>2.917322944660824</v>
+        <v>2.9173229446608242</v>
       </c>
       <c r="I44">
-        <v>26.4120002746582</v>
+        <v>26.412000274658201</v>
       </c>
       <c r="J44">
         <v>23.36775002479553</v>
       </c>
       <c r="K44">
-        <v>17.41450002670288</v>
+        <v>17.414500026702878</v>
       </c>
       <c r="L44">
-        <v>12.50642498016357</v>
+        <v>12.506424980163571</v>
       </c>
       <c r="M44">
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="N44">
         <v>1.52</v>
@@ -5958,7 +5981,7 @@
         <v>0</v>
       </c>
       <c r="T44">
-        <v>1.111111111111111</v>
+        <v>1.1111111111111109</v>
       </c>
       <c r="U44" t="b">
         <v>0</v>
@@ -6006,7 +6029,7 @@
         <v>217</v>
       </c>
       <c r="AK44">
-        <v>32.60088955793161</v>
+        <v>32.600889557931609</v>
       </c>
     </row>
     <row r="45" spans="1:37">
@@ -6020,34 +6043,34 @@
         <v>1267</v>
       </c>
       <c r="D45">
-        <v>36.23</v>
+        <v>36.229999999999997</v>
       </c>
       <c r="E45">
         <v>6.93</v>
       </c>
       <c r="F45">
-        <v>1.571661158635942</v>
+        <v>1.5716611586359419</v>
       </c>
       <c r="G45">
         <v>4.45</v>
       </c>
       <c r="H45">
-        <v>1.244809717328161</v>
+        <v>1.2448097173281609</v>
       </c>
       <c r="I45">
-        <v>37.20400009155274</v>
+        <v>37.204000091552743</v>
       </c>
       <c r="J45">
-        <v>33.59249963760376</v>
+        <v>33.592499637603758</v>
       </c>
       <c r="K45">
-        <v>28.52159984588623</v>
+        <v>28.521599845886229</v>
       </c>
       <c r="L45">
         <v>22.00894994258881</v>
       </c>
       <c r="M45">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="N45">
         <v>1.3</v>
@@ -6095,7 +6118,7 @@
         <v>255.92</v>
       </c>
       <c r="AD45">
-        <v>9.970000000000001</v>
+        <v>9.9700000000000006</v>
       </c>
       <c r="AE45">
         <v>-27.27</v>
@@ -6116,7 +6139,7 @@
         <v>216</v>
       </c>
       <c r="AK45">
-        <v>31.90120071852455</v>
+        <v>31.901200718524549</v>
       </c>
     </row>
     <row r="46" spans="1:37">
@@ -6124,7 +6147,7 @@
         <v>81</v>
       </c>
       <c r="B46">
-        <v>92.5257731958763</v>
+        <v>92.525773195876297</v>
       </c>
       <c r="C46">
         <v>1870</v>
@@ -6142,19 +6165,19 @@
         <v>1.04</v>
       </c>
       <c r="H46">
-        <v>-1.458161896512778</v>
+        <v>-1.4581618965127781</v>
       </c>
       <c r="I46">
         <v>202.6420013427734</v>
       </c>
       <c r="J46">
-        <v>196.6124992370605</v>
+        <v>196.61249923706049</v>
       </c>
       <c r="K46">
-        <v>189.285998840332</v>
+        <v>189.28599884033201</v>
       </c>
       <c r="L46">
-        <v>145.3688497924805</v>
+        <v>145.36884979248049</v>
       </c>
       <c r="M46">
         <v>1.03</v>
@@ -6196,13 +6219,13 @@
         <v>12.35</v>
       </c>
       <c r="AA46">
-        <v>-285.71</v>
+        <v>-285.70999999999998</v>
       </c>
       <c r="AB46">
         <v>95.86</v>
       </c>
       <c r="AC46">
-        <v>163.64</v>
+        <v>163.63999999999999</v>
       </c>
       <c r="AD46">
         <v>1.25</v>
@@ -6211,10 +6234,10 @@
         <v>400</v>
       </c>
       <c r="AF46">
-        <v>-158.33</v>
+        <v>-158.33000000000001</v>
       </c>
       <c r="AG46">
-        <v>136.36</v>
+        <v>136.36000000000001</v>
       </c>
       <c r="AH46" t="s">
         <v>161</v>
@@ -6234,7 +6257,7 @@
         <v>82</v>
       </c>
       <c r="B47">
-        <v>97.27107337780473</v>
+        <v>97.271073377804726</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -6246,19 +6269,19 @@
         <v>2.41</v>
       </c>
       <c r="F47">
-        <v>-0.5772079415346232</v>
+        <v>-0.57720794153462318</v>
       </c>
       <c r="G47">
-        <v>2.53</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="H47">
-        <v>-0.2770980535148309</v>
+        <v>-0.27709805351483091</v>
       </c>
       <c r="I47">
-        <v>137.0320007324219</v>
+        <v>137.03200073242189</v>
       </c>
       <c r="J47">
-        <v>142.6734992980957</v>
+        <v>142.67349929809569</v>
       </c>
       <c r="K47">
         <v>136.1175996398926</v>
@@ -6300,7 +6323,7 @@
         <v>45.01</v>
       </c>
       <c r="Y47">
-        <v>152.89</v>
+        <v>152.88999999999999</v>
       </c>
       <c r="Z47">
         <v>3433.99</v>
@@ -6309,7 +6332,7 @@
         <v>48.4</v>
       </c>
       <c r="AB47">
-        <v>128.05</v>
+        <v>128.05000000000001</v>
       </c>
       <c r="AC47">
         <v>110.31</v>
@@ -6344,7 +6367,7 @@
         <v>83</v>
       </c>
       <c r="B48">
-        <v>91.22195269860521</v>
+        <v>91.221952698605207</v>
       </c>
       <c r="C48">
         <v>2205</v>
@@ -6356,16 +6379,16 @@
         <v>3.35</v>
       </c>
       <c r="F48">
-        <v>-0.1303192348619835</v>
+        <v>-0.13031923486198349</v>
       </c>
       <c r="G48">
         <v>2.13</v>
       </c>
       <c r="H48">
-        <v>-0.5941621724404541</v>
+        <v>-0.59416217244045411</v>
       </c>
       <c r="I48">
-        <v>116.2440002441406</v>
+        <v>116.24400024414059</v>
       </c>
       <c r="J48">
         <v>114.1310005187988</v>
@@ -6374,13 +6397,13 @@
         <v>104.7096005249023</v>
       </c>
       <c r="L48">
-        <v>86.76559997558594</v>
+        <v>86.765599975585943</v>
       </c>
       <c r="M48">
         <v>1.02</v>
       </c>
       <c r="N48">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="P48">
         <v>1</v>
@@ -6395,7 +6418,7 @@
         <v>0</v>
       </c>
       <c r="T48">
-        <v>2.777777777777778</v>
+        <v>2.7777777777777781</v>
       </c>
       <c r="U48" t="b">
         <v>1</v>
@@ -6422,7 +6445,7 @@
         <v>40.46</v>
       </c>
       <c r="AC48">
-        <v>158.58</v>
+        <v>158.58000000000001</v>
       </c>
       <c r="AD48">
         <v>12.03</v>
@@ -6446,7 +6469,7 @@
         <v>217</v>
       </c>
       <c r="AK48">
-        <v>31.31175191022695</v>
+        <v>31.311751910226949</v>
       </c>
     </row>
     <row r="49" spans="1:37">
@@ -6454,7 +6477,7 @@
         <v>84</v>
       </c>
       <c r="B49">
-        <v>97.98362644026682</v>
+        <v>97.983626440266818</v>
       </c>
       <c r="C49">
         <v>3277</v>
@@ -6466,25 +6489,25 @@
         <v>4.12</v>
       </c>
       <c r="F49">
-        <v>0.2357491737953916</v>
+        <v>0.23574917379539159</v>
       </c>
       <c r="G49">
         <v>3.23</v>
       </c>
       <c r="H49">
-        <v>0.2777641546050101</v>
+        <v>0.27776415460501008</v>
       </c>
       <c r="I49">
-        <v>156.9940002441406</v>
+        <v>156.99400024414061</v>
       </c>
       <c r="J49">
-        <v>151.353498840332</v>
+        <v>151.35349884033201</v>
       </c>
       <c r="K49">
-        <v>130.0905995178223</v>
+        <v>130.09059951782231</v>
       </c>
       <c r="L49">
-        <v>82.54389993667603</v>
+        <v>82.543899936676027</v>
       </c>
       <c r="M49">
         <v>1.04</v>
@@ -6523,7 +6546,7 @@
         <v>165.33</v>
       </c>
       <c r="Z49">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="AA49">
         <v>-564.01</v>
@@ -6564,13 +6587,13 @@
         <v>85</v>
       </c>
       <c r="B50">
-        <v>93.73862947240752</v>
+        <v>93.738629472407524</v>
       </c>
       <c r="C50">
         <v>2489</v>
       </c>
       <c r="D50">
-        <v>98.76000000000001</v>
+        <v>98.76</v>
       </c>
       <c r="E50">
         <v>1.46</v>
@@ -6585,22 +6608,22 @@
         <v>-1.212437204345419</v>
       </c>
       <c r="I50">
-        <v>98.94200134277345</v>
+        <v>98.942001342773452</v>
       </c>
       <c r="J50">
-        <v>96.75800018310547</v>
+        <v>96.758000183105466</v>
       </c>
       <c r="K50">
-        <v>87.53620010375977</v>
+        <v>87.536200103759768</v>
       </c>
       <c r="L50">
-        <v>68.34769990921021</v>
+        <v>68.347699909210206</v>
       </c>
       <c r="M50">
         <v>1.02</v>
       </c>
       <c r="N50">
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="P50">
         <v>0</v>
@@ -6666,7 +6689,7 @@
         <v>228</v>
       </c>
       <c r="AK50">
-        <v>29.87582807332288</v>
+        <v>29.875828073322879</v>
       </c>
     </row>
     <row r="51" spans="1:37">
@@ -6674,7 +6697,7 @@
         <v>86</v>
       </c>
       <c r="B51">
-        <v>95.26986052152819</v>
+        <v>95.269860521528187</v>
       </c>
       <c r="C51">
         <v>1452</v>
@@ -6686,19 +6709,19 @@
         <v>2.95</v>
       </c>
       <c r="F51">
-        <v>-0.3204846419567237</v>
+        <v>-0.32048464195672371</v>
       </c>
       <c r="G51">
         <v>2.04</v>
       </c>
       <c r="H51">
-        <v>-0.6655015991987193</v>
+        <v>-0.66550159919871932</v>
       </c>
       <c r="I51">
-        <v>190.4019958496094</v>
+        <v>190.40199584960939</v>
       </c>
       <c r="J51">
-        <v>180.2029991149902</v>
+        <v>180.20299911499021</v>
       </c>
       <c r="K51">
         <v>159.9797998046875</v>
@@ -6761,7 +6784,7 @@
         <v>0.6</v>
       </c>
       <c r="AF51">
-        <v>2.45</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="AG51">
         <v>8.67</v>
@@ -6776,7 +6799,7 @@
         <v>217</v>
       </c>
       <c r="AK51">
-        <v>28.88449153490319</v>
+        <v>28.884491534903191</v>
       </c>
     </row>
     <row r="52" spans="1:37">
@@ -6784,7 +6807,7 @@
         <v>87</v>
       </c>
       <c r="B52">
-        <v>96.22498483929654</v>
+        <v>96.224984839296539</v>
       </c>
       <c r="C52">
         <v>2515</v>
@@ -6796,22 +6819,22 @@
         <v>1.65</v>
       </c>
       <c r="F52">
-        <v>-0.9385222150146298</v>
+        <v>-0.93852221501462985</v>
       </c>
       <c r="G52">
         <v>4.58</v>
       </c>
       <c r="H52">
-        <v>1.347855555978989</v>
+        <v>1.3478555559789891</v>
       </c>
       <c r="I52">
-        <v>26.61599998474121</v>
+        <v>26.615999984741212</v>
       </c>
       <c r="J52">
-        <v>25.42649984359741</v>
+        <v>25.426499843597409</v>
       </c>
       <c r="K52">
-        <v>21.4167998123169</v>
+        <v>21.416799812316899</v>
       </c>
       <c r="L52">
         <v>17.4421999502182</v>
@@ -6856,7 +6879,7 @@
         <v>1.47</v>
       </c>
       <c r="AA52">
-        <v>-2.24</v>
+        <v>-2.2400000000000002</v>
       </c>
       <c r="AB52">
         <v>40.33</v>
@@ -6894,7 +6917,7 @@
         <v>88</v>
       </c>
       <c r="B53">
-        <v>94.36021831412977</v>
+        <v>94.360218314129767</v>
       </c>
       <c r="C53">
         <v>2445</v>
@@ -6906,28 +6929,28 @@
         <v>6.44</v>
       </c>
       <c r="F53">
-        <v>1.338708534944885</v>
+        <v>1.3387085349448851</v>
       </c>
       <c r="G53">
         <v>4.5</v>
       </c>
       <c r="H53">
-        <v>1.284442732193864</v>
+        <v>1.2844427321938641</v>
       </c>
       <c r="I53">
-        <v>37.99800033569336</v>
+        <v>37.998000335693362</v>
       </c>
       <c r="J53">
-        <v>32.63450012207031</v>
+        <v>32.634500122070307</v>
       </c>
       <c r="K53">
-        <v>26.78540008544922</v>
+        <v>26.785400085449218</v>
       </c>
       <c r="L53">
-        <v>21.80339999675751</v>
+        <v>21.803399996757509</v>
       </c>
       <c r="M53">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="N53">
         <v>1.42</v>
@@ -6975,7 +6998,7 @@
         <v>122.64</v>
       </c>
       <c r="AD53">
-        <v>9.119999999999999</v>
+        <v>9.1199999999999992</v>
       </c>
       <c r="AE53">
         <v>50</v>
@@ -6996,7 +7019,7 @@
         <v>225</v>
       </c>
       <c r="AK53">
-        <v>28.16913146126526</v>
+        <v>28.169131461265259</v>
       </c>
     </row>
     <row r="54" spans="1:37">
@@ -7004,7 +7027,7 @@
         <v>89</v>
       </c>
       <c r="B54">
-        <v>90.72164948453609</v>
+        <v>90.721649484536087</v>
       </c>
       <c r="C54">
         <v>227</v>
@@ -7016,16 +7039,16 @@
         <v>2.46</v>
       </c>
       <c r="F54">
-        <v>-0.5534372656477807</v>
+        <v>-0.55343726564778073</v>
       </c>
       <c r="G54">
         <v>2.73</v>
       </c>
       <c r="H54">
-        <v>-0.1185659940520191</v>
+        <v>-0.11856599405201911</v>
       </c>
       <c r="I54">
-        <v>27.29799995422363</v>
+        <v>27.297999954223631</v>
       </c>
       <c r="J54">
         <v>26.89500007629395</v>
@@ -7034,13 +7057,13 @@
         <v>24.24099994659424</v>
       </c>
       <c r="L54">
-        <v>19.54550009727478</v>
+        <v>19.545500097274779</v>
       </c>
       <c r="M54">
         <v>1.01</v>
       </c>
       <c r="N54">
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="P54">
         <v>0</v>
@@ -7076,16 +7099,16 @@
         <v>11.62</v>
       </c>
       <c r="AA54">
-        <v>-38.02</v>
+        <v>-38.020000000000003</v>
       </c>
       <c r="AB54">
-        <v>137.42</v>
+        <v>137.41999999999999</v>
       </c>
       <c r="AC54">
         <v>36.43</v>
       </c>
       <c r="AD54">
-        <v>69.79000000000001</v>
+        <v>69.790000000000006</v>
       </c>
       <c r="AE54">
         <v>184.21</v>
@@ -7106,7 +7129,7 @@
         <v>237</v>
       </c>
       <c r="AK54">
-        <v>27.32840294284461</v>
+        <v>27.328402942844608</v>
       </c>
     </row>
     <row r="55" spans="1:37">
@@ -7126,25 +7149,25 @@
         <v>2.52</v>
       </c>
       <c r="F55">
-        <v>-0.5249124545835696</v>
+        <v>-0.52491245458356961</v>
       </c>
       <c r="G55">
         <v>2.17</v>
       </c>
       <c r="H55">
-        <v>-0.5624557605478918</v>
+        <v>-0.56245576054789181</v>
       </c>
       <c r="I55">
-        <v>195.4640014648438</v>
+        <v>195.46400146484379</v>
       </c>
       <c r="J55">
-        <v>194.5599998474121</v>
+        <v>194.55999984741209</v>
       </c>
       <c r="K55">
-        <v>187.7383996582031</v>
+        <v>187.73839965820309</v>
       </c>
       <c r="L55">
-        <v>165.5745502471924</v>
+        <v>165.57455024719241</v>
       </c>
       <c r="M55">
         <v>1</v>
@@ -7192,7 +7215,7 @@
         <v>31.42</v>
       </c>
       <c r="AC55">
-        <v>37.88</v>
+        <v>37.880000000000003</v>
       </c>
       <c r="AD55">
         <v>20.87</v>
@@ -7216,7 +7239,7 @@
         <v>238</v>
       </c>
       <c r="AK55">
-        <v>27.31123156698346</v>
+        <v>27.311231566983459</v>
       </c>
     </row>
     <row r="56" spans="1:37">
@@ -7230,22 +7253,22 @@
         <v>1002</v>
       </c>
       <c r="D56">
-        <v>17.19</v>
+        <v>17.190000000000001</v>
       </c>
       <c r="E56">
         <v>4.3</v>
       </c>
       <c r="F56">
-        <v>0.3213236069880246</v>
+        <v>0.32132360698802459</v>
       </c>
       <c r="G56">
         <v>3.49</v>
       </c>
       <c r="H56">
-        <v>0.4838558319066654</v>
+        <v>0.48385583190666542</v>
       </c>
       <c r="I56">
-        <v>16.77800064086914</v>
+        <v>16.778000640869141</v>
       </c>
       <c r="J56">
         <v>15.59650001525879</v>
@@ -7254,7 +7277,7 @@
         <v>13.73320001602173</v>
       </c>
       <c r="L56">
-        <v>12.41670000553131</v>
+        <v>12.416700005531309</v>
       </c>
       <c r="M56">
         <v>1.08</v>
@@ -7287,7 +7310,7 @@
         <v>1</v>
       </c>
       <c r="X56">
-        <v>8.039999999999999</v>
+        <v>8.0399999999999991</v>
       </c>
       <c r="Y56">
         <v>18.38</v>
@@ -7299,13 +7322,13 @@
         <v>1.08</v>
       </c>
       <c r="AB56">
-        <v>40.87</v>
+        <v>40.869999999999997</v>
       </c>
       <c r="AC56">
         <v>127.59</v>
       </c>
       <c r="AD56">
-        <v>2.51</v>
+        <v>2.5099999999999998</v>
       </c>
       <c r="AE56">
         <v>500</v>
@@ -7314,7 +7337,7 @@
         <v>92.31</v>
       </c>
       <c r="AG56">
-        <v>-156.52</v>
+        <v>-156.52000000000001</v>
       </c>
       <c r="AH56" t="s">
         <v>178</v>
@@ -7326,7 +7349,7 @@
         <v>239</v>
       </c>
       <c r="AK56">
-        <v>27.29688257866937</v>
+        <v>27.296882578669369</v>
       </c>
     </row>
     <row r="57" spans="1:37">
@@ -7334,34 +7357,34 @@
         <v>92</v>
       </c>
       <c r="B57">
-        <v>95.9066100667071</v>
+        <v>95.906610066707103</v>
       </c>
       <c r="C57">
         <v>459</v>
       </c>
       <c r="D57">
-        <v>36.02</v>
+        <v>36.020000000000003</v>
       </c>
       <c r="E57">
-        <v>2.18</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="F57">
-        <v>-0.6865530506140988</v>
+        <v>-0.68655305061409877</v>
       </c>
       <c r="G57">
         <v>1.87</v>
       </c>
       <c r="H57">
-        <v>-0.8002538497421091</v>
+        <v>-0.80025384974210911</v>
       </c>
       <c r="I57">
-        <v>34.1620002746582</v>
+        <v>34.162000274658197</v>
       </c>
       <c r="J57">
         <v>32.38850030899048</v>
       </c>
       <c r="K57">
-        <v>29.92900012969971</v>
+        <v>29.929000129699709</v>
       </c>
       <c r="L57">
         <v>23.03400001525879</v>
@@ -7370,7 +7393,7 @@
         <v>1.05</v>
       </c>
       <c r="N57">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="P57">
         <v>0</v>
@@ -7412,13 +7435,13 @@
         <v>53.35</v>
       </c>
       <c r="AC57">
-        <v>94.76000000000001</v>
+        <v>94.76</v>
       </c>
       <c r="AD57">
         <v>53.37</v>
       </c>
       <c r="AE57">
-        <v>316.22</v>
+        <v>316.22000000000003</v>
       </c>
       <c r="AF57">
         <v>85</v>
@@ -7436,7 +7459,7 @@
         <v>232</v>
       </c>
       <c r="AK57">
-        <v>27.20328168561523</v>
+        <v>27.203281685615231</v>
       </c>
     </row>
     <row r="58" spans="1:37">
@@ -7444,7 +7467,7 @@
         <v>93</v>
       </c>
       <c r="B58">
-        <v>95.20921770770163</v>
+        <v>95.209217707701626</v>
       </c>
       <c r="C58">
         <v>2629</v>
@@ -7456,31 +7479,31 @@
         <v>2.12</v>
       </c>
       <c r="F58">
-        <v>-0.7150778616783099</v>
+        <v>-0.71507786167830989</v>
       </c>
       <c r="G58">
         <v>1.79</v>
       </c>
       <c r="H58">
-        <v>-0.8636666735272339</v>
+        <v>-0.86366667352723392</v>
       </c>
       <c r="I58">
         <v>509.7860046386719</v>
       </c>
       <c r="J58">
-        <v>505.0490036010742</v>
+        <v>505.04900360107422</v>
       </c>
       <c r="K58">
-        <v>466.215400390625</v>
+        <v>466.21540039062501</v>
       </c>
       <c r="L58">
-        <v>386.1536998748779</v>
+        <v>386.15369987487787</v>
       </c>
       <c r="M58">
         <v>1.01</v>
       </c>
       <c r="N58">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="P58">
         <v>2</v>
@@ -7495,7 +7518,7 @@
         <v>0</v>
       </c>
       <c r="T58">
-        <v>1.111111111111111</v>
+        <v>1.1111111111111109</v>
       </c>
       <c r="U58" t="b">
         <v>1</v>
@@ -7554,7 +7577,7 @@
         <v>94</v>
       </c>
       <c r="B59">
-        <v>94.45118253486962</v>
+        <v>94.451182534869616</v>
       </c>
       <c r="C59">
         <v>813</v>
@@ -7566,13 +7589,13 @@
         <v>3.19</v>
       </c>
       <c r="F59">
-        <v>-0.2063853976998797</v>
+        <v>-0.20638539769987971</v>
       </c>
       <c r="G59">
         <v>2.09</v>
       </c>
       <c r="H59">
-        <v>-0.6258685843330165</v>
+        <v>-0.62586858433301651</v>
       </c>
       <c r="I59">
         <v>117.1579986572266</v>
@@ -7581,16 +7604,16 @@
         <v>113.9735000610352</v>
       </c>
       <c r="K59">
-        <v>106.7423999023437</v>
+        <v>106.74239990234371</v>
       </c>
       <c r="L59">
-        <v>86.10434984207153</v>
+        <v>86.104349842071528</v>
       </c>
       <c r="M59">
         <v>1.03</v>
       </c>
       <c r="N59">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="P59">
         <v>2</v>
@@ -7605,7 +7628,7 @@
         <v>0</v>
       </c>
       <c r="T59">
-        <v>1.111111111111111</v>
+        <v>1.1111111111111109</v>
       </c>
       <c r="U59" t="b">
         <v>1</v>
@@ -7656,7 +7679,7 @@
         <v>231</v>
       </c>
       <c r="AK59">
-        <v>27.07999138249136</v>
+        <v>27.079991382491361</v>
       </c>
     </row>
     <row r="60" spans="1:37">
@@ -7664,7 +7687,7 @@
         <v>95</v>
       </c>
       <c r="B60">
-        <v>95.8308065494239</v>
+        <v>95.830806549423897</v>
       </c>
       <c r="C60">
         <v>1156</v>
@@ -7676,16 +7699,16 @@
         <v>3.56</v>
       </c>
       <c r="F60">
-        <v>-0.03048239613724486</v>
+        <v>-3.048239613724486E-2</v>
       </c>
       <c r="G60">
         <v>3.2</v>
       </c>
       <c r="H60">
-        <v>0.2539843456855885</v>
+        <v>0.25398434568558848</v>
       </c>
       <c r="I60">
-        <v>16.37399978637695</v>
+        <v>16.373999786376949</v>
       </c>
       <c r="J60">
         <v>15.48299989700317</v>
@@ -7730,7 +7753,7 @@
         <v>6.16</v>
       </c>
       <c r="Y60">
-        <v>17.15</v>
+        <v>17.149999999999999</v>
       </c>
       <c r="Z60">
         <v>1.87</v>
@@ -7745,7 +7768,7 @@
         <v>176.47</v>
       </c>
       <c r="AD60">
-        <v>4.06</v>
+        <v>4.0599999999999996</v>
       </c>
       <c r="AE60">
         <v>0</v>
@@ -7766,7 +7789,7 @@
         <v>229</v>
       </c>
       <c r="AK60">
-        <v>27.06740974429607</v>
+        <v>27.067409744296071</v>
       </c>
     </row>
     <row r="61" spans="1:37">
@@ -7774,7 +7797,7 @@
         <v>96</v>
       </c>
       <c r="B61">
-        <v>93.6173438447544</v>
+        <v>93.617343844754402</v>
       </c>
       <c r="C61">
         <v>1974</v>
@@ -7792,25 +7815,25 @@
         <v>2.13</v>
       </c>
       <c r="H61">
-        <v>-0.5941621724404541</v>
+        <v>-0.59416217244045411</v>
       </c>
       <c r="I61">
-        <v>57.24599990844727</v>
+        <v>57.245999908447267</v>
       </c>
       <c r="J61">
-        <v>55.79349994659424</v>
+        <v>55.793499946594238</v>
       </c>
       <c r="K61">
-        <v>52.58559989929199</v>
+        <v>52.585599899291992</v>
       </c>
       <c r="L61">
-        <v>41.83829998016358</v>
+        <v>41.838299980163583</v>
       </c>
       <c r="M61">
         <v>1.03</v>
       </c>
       <c r="N61">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="P61">
         <v>0</v>
@@ -7849,7 +7872,7 @@
         <v>13.76</v>
       </c>
       <c r="AB61">
-        <v>39.88</v>
+        <v>39.880000000000003</v>
       </c>
       <c r="AC61">
         <v>120.69</v>
@@ -7896,7 +7919,7 @@
         <v>6.44</v>
       </c>
       <c r="F62">
-        <v>1.338708534944885</v>
+        <v>1.3387085349448851</v>
       </c>
       <c r="G62">
         <v>4.22</v>
@@ -7905,19 +7928,19 @@
         <v>1.062497848945928</v>
       </c>
       <c r="I62">
-        <v>53.2520004272461</v>
+        <v>53.252000427246102</v>
       </c>
       <c r="J62">
-        <v>47.56900024414062</v>
+        <v>47.569000244140618</v>
       </c>
       <c r="K62">
-        <v>39.10380001068116</v>
+        <v>39.103800010681162</v>
       </c>
       <c r="L62">
         <v>35.41809998512268</v>
       </c>
       <c r="M62">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="N62">
         <v>1.36</v>
@@ -7953,7 +7976,7 @@
         <v>54.94</v>
       </c>
       <c r="Z62">
-        <v>8.449999999999999</v>
+        <v>8.4499999999999993</v>
       </c>
       <c r="AA62">
         <v>-53.03</v>
@@ -7994,7 +8017,7 @@
         <v>98</v>
       </c>
       <c r="B63">
-        <v>94.98180715585202</v>
+        <v>94.981807155852024</v>
       </c>
       <c r="C63">
         <v>980</v>
@@ -8006,31 +8029,31 @@
         <v>4.25</v>
       </c>
       <c r="F63">
-        <v>0.2975529311011821</v>
+        <v>0.29755293110118208</v>
       </c>
       <c r="G63">
         <v>3.44</v>
       </c>
       <c r="H63">
-        <v>0.4442228170409623</v>
+        <v>0.44422281704096228</v>
       </c>
       <c r="I63">
-        <v>36.34000015258789</v>
+        <v>36.340000152587891</v>
       </c>
       <c r="J63">
         <v>33.41425008773804</v>
       </c>
       <c r="K63">
-        <v>32.52310001373291</v>
+        <v>32.523100013732908</v>
       </c>
       <c r="L63">
         <v>23.1948250246048</v>
       </c>
       <c r="M63">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="N63">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="P63">
         <v>0</v>
@@ -8096,7 +8119,7 @@
         <v>227</v>
       </c>
       <c r="AK63">
-        <v>26.72536323889098</v>
+        <v>26.725363238890981</v>
       </c>
     </row>
     <row r="64" spans="1:37">
@@ -8104,7 +8127,7 @@
         <v>99</v>
       </c>
       <c r="B64">
-        <v>90.05457853244391</v>
+        <v>90.054578532443912</v>
       </c>
       <c r="C64">
         <v>311</v>
@@ -8116,31 +8139,31 @@
         <v>1.84</v>
       </c>
       <c r="F64">
-        <v>-0.848193646644628</v>
+        <v>-0.84819364664462804</v>
       </c>
       <c r="G64">
         <v>1.66</v>
       </c>
       <c r="H64">
-        <v>-0.9667125121780615</v>
+        <v>-0.96671251217806153</v>
       </c>
       <c r="I64">
-        <v>20.89599990844727</v>
+        <v>20.895999908447269</v>
       </c>
       <c r="J64">
-        <v>19.71499986648559</v>
+        <v>19.714999866485591</v>
       </c>
       <c r="K64">
-        <v>18.76879993438721</v>
+        <v>18.768799934387211</v>
       </c>
       <c r="L64">
-        <v>16.42849996089935</v>
+        <v>16.428499960899352</v>
       </c>
       <c r="M64">
         <v>1.06</v>
       </c>
       <c r="N64">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="P64">
         <v>0</v>
@@ -8155,7 +8178,7 @@
         <v>0</v>
       </c>
       <c r="T64">
-        <v>2.222222222222222</v>
+        <v>2.2222222222222219</v>
       </c>
       <c r="U64" t="b">
         <v>0</v>
@@ -8194,7 +8217,7 @@
         <v>296.61</v>
       </c>
       <c r="AG64">
-        <v>-310.71</v>
+        <v>-310.70999999999998</v>
       </c>
       <c r="AH64" t="s">
         <v>187</v>
@@ -8226,31 +8249,31 @@
         <v>3.07</v>
       </c>
       <c r="F65">
-        <v>-0.2634350198283018</v>
+        <v>-0.26343501982830181</v>
       </c>
       <c r="G65">
         <v>2.67</v>
       </c>
       <c r="H65">
-        <v>-0.1661256118908626</v>
+        <v>-0.16612561189086261</v>
       </c>
       <c r="I65">
         <v>194.9</v>
       </c>
       <c r="J65">
-        <v>180.7950004577637</v>
+        <v>180.79500045776371</v>
       </c>
       <c r="K65">
-        <v>167.4760006713867</v>
+        <v>167.47600067138671</v>
       </c>
       <c r="L65">
-        <v>120.3206001281738</v>
+        <v>120.32060012817379</v>
       </c>
       <c r="M65">
         <v>1.08</v>
       </c>
       <c r="N65">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="P65">
         <v>0</v>
@@ -8283,7 +8306,7 @@
         <v>198.24</v>
       </c>
       <c r="Z65">
-        <v>8.699999999999999</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="AA65">
         <v>1.52</v>
@@ -8292,7 +8315,7 @@
         <v>46.87</v>
       </c>
       <c r="AC65">
-        <v>90.31999999999999</v>
+        <v>90.32</v>
       </c>
       <c r="AD65">
         <v>14.69</v>
@@ -8316,7 +8339,7 @@
         <v>241</v>
       </c>
       <c r="AK65">
-        <v>26.49720003804721</v>
+        <v>26.497200038047211</v>
       </c>
     </row>
     <row r="66" spans="1:37">
@@ -8324,7 +8347,7 @@
         <v>101</v>
       </c>
       <c r="B66">
-        <v>91.67677380230442</v>
+        <v>91.676773802304425</v>
       </c>
       <c r="C66">
         <v>476</v>
@@ -8336,31 +8359,31 @@
         <v>3.22</v>
       </c>
       <c r="F66">
-        <v>-0.192122992167774</v>
+        <v>-0.19212299216777401</v>
       </c>
       <c r="G66">
         <v>2.08</v>
       </c>
       <c r="H66">
-        <v>-0.6337951873061569</v>
+        <v>-0.63379518730615692</v>
       </c>
       <c r="I66">
-        <v>130.0380004882813</v>
+        <v>130.03800048828131</v>
       </c>
       <c r="J66">
-        <v>126.0159992218018</v>
+        <v>126.01599922180181</v>
       </c>
       <c r="K66">
-        <v>119.6036000061035</v>
+        <v>119.60360000610351</v>
       </c>
       <c r="L66">
-        <v>98.99699993133545</v>
+        <v>98.996999931335452</v>
       </c>
       <c r="M66">
         <v>1.03</v>
       </c>
       <c r="N66">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="P66">
         <v>0</v>
@@ -8390,7 +8413,7 @@
         <v>61.47</v>
       </c>
       <c r="Y66">
-        <v>136.14</v>
+        <v>136.13999999999999</v>
       </c>
       <c r="Z66">
         <v>61.18</v>
@@ -8426,7 +8449,7 @@
         <v>210</v>
       </c>
       <c r="AK66">
-        <v>26.41763745231391</v>
+        <v>26.417637452313912</v>
       </c>
     </row>
     <row r="67" spans="1:37">
@@ -8434,7 +8457,7 @@
         <v>102</v>
       </c>
       <c r="B67">
-        <v>94.7847180109157</v>
+        <v>94.784718010915697</v>
       </c>
       <c r="C67">
         <v>837</v>
@@ -8446,31 +8469,31 @@
         <v>8.74</v>
       </c>
       <c r="F67">
-        <v>2.432159625739642</v>
+        <v>2.4321596257396418</v>
       </c>
       <c r="G67">
         <v>5.18</v>
       </c>
       <c r="H67">
-        <v>1.823451734367424</v>
+        <v>1.8234517343674239</v>
       </c>
       <c r="I67">
-        <v>52.41800003051758</v>
+        <v>52.418000030517582</v>
       </c>
       <c r="J67">
         <v>50.66549987792969</v>
       </c>
       <c r="K67">
-        <v>45.86760002136231</v>
+        <v>45.867600021362307</v>
       </c>
       <c r="L67">
-        <v>33.25565001487732</v>
+        <v>33.255650014877318</v>
       </c>
       <c r="M67">
         <v>1.03</v>
       </c>
       <c r="N67">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="P67">
         <v>2</v>
@@ -8485,7 +8508,7 @@
         <v>0</v>
       </c>
       <c r="T67">
-        <v>4.444444444444444</v>
+        <v>4.4444444444444438</v>
       </c>
       <c r="U67" t="b">
         <v>0</v>
@@ -8536,7 +8559,7 @@
         <v>242</v>
       </c>
       <c r="AK67">
-        <v>26.21556804959812</v>
+        <v>26.215568049598119</v>
       </c>
     </row>
     <row r="68" spans="1:37">
@@ -8544,7 +8567,7 @@
         <v>103</v>
       </c>
       <c r="B68">
-        <v>94.23893268647664</v>
+        <v>94.238932686476645</v>
       </c>
       <c r="C68">
         <v>4210</v>
@@ -8556,13 +8579,13 @@
         <v>2.68</v>
       </c>
       <c r="F68">
-        <v>-0.4488462917456734</v>
+        <v>-0.44884629174567342</v>
       </c>
       <c r="G68">
         <v>2.42</v>
       </c>
       <c r="H68">
-        <v>-0.3642906862193772</v>
+        <v>-0.36429068621937721</v>
       </c>
       <c r="I68">
         <v>26.04699974060059</v>
@@ -8571,10 +8594,10 @@
         <v>24.7227499961853</v>
       </c>
       <c r="K68">
-        <v>21.71009998321533</v>
+        <v>21.710099983215329</v>
       </c>
       <c r="L68">
-        <v>16.52364998817444</v>
+        <v>16.523649988174441</v>
       </c>
       <c r="M68">
         <v>1.05</v>
@@ -8613,7 +8636,7 @@
         <v>27</v>
       </c>
       <c r="Z68">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="AA68" t="s">
         <v>157</v>
@@ -8654,7 +8677,7 @@
         <v>104</v>
       </c>
       <c r="B69">
-        <v>92.1922377198302</v>
+        <v>92.192237719830203</v>
       </c>
       <c r="C69">
         <v>2719</v>
@@ -8663,34 +8686,34 @@
         <v>31.06</v>
       </c>
       <c r="E69">
-        <v>2.26</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="F69">
-        <v>-0.648519969195151</v>
+        <v>-0.64851996919515098</v>
       </c>
       <c r="G69">
         <v>2.56</v>
       </c>
       <c r="H69">
-        <v>-0.253318244595409</v>
+        <v>-0.25331824459540903</v>
       </c>
       <c r="I69">
-        <v>31.14600028991699</v>
+        <v>31.146000289916991</v>
       </c>
       <c r="J69">
-        <v>29.99149980545044</v>
+        <v>29.991499805450442</v>
       </c>
       <c r="K69">
         <v>28.55799991607666</v>
       </c>
       <c r="L69">
-        <v>25.65859999656677</v>
+        <v>25.658599996566771</v>
       </c>
       <c r="M69">
         <v>1.04</v>
       </c>
       <c r="N69">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="P69">
         <v>0</v>
@@ -8776,19 +8799,19 @@
         <v>1.88</v>
       </c>
       <c r="F70">
-        <v>-0.8291771059351541</v>
+        <v>-0.82917710593515415</v>
       </c>
       <c r="G70">
         <v>2.11</v>
       </c>
       <c r="H70">
-        <v>-0.6100153783867354</v>
+        <v>-0.61001537838673536</v>
       </c>
       <c r="I70">
-        <v>140.9799987792969</v>
+        <v>140.97999877929689</v>
       </c>
       <c r="J70">
-        <v>137.3864990234375</v>
+        <v>137.38649902343749</v>
       </c>
       <c r="K70">
         <v>123.5525994873047</v>
@@ -8800,7 +8823,7 @@
         <v>1.03</v>
       </c>
       <c r="N70">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="P70">
         <v>0</v>
@@ -8854,7 +8877,7 @@
         <v>45.71</v>
       </c>
       <c r="AG70">
-        <v>-34.38</v>
+        <v>-34.380000000000003</v>
       </c>
       <c r="AH70" t="s">
         <v>169</v>
@@ -8866,7 +8889,7 @@
         <v>245</v>
       </c>
       <c r="AK70">
-        <v>23.75665149620352</v>
+        <v>23.756651496203521</v>
       </c>
     </row>
     <row r="71" spans="1:37">
@@ -8874,7 +8897,7 @@
         <v>106</v>
       </c>
       <c r="B71">
-        <v>95.07277137659187</v>
+        <v>95.072771376591874</v>
       </c>
       <c r="C71">
         <v>4198</v>
@@ -8883,34 +8906,34 @@
         <v>416.41</v>
       </c>
       <c r="E71">
-        <v>2.18</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="F71">
-        <v>-0.6865530506140988</v>
+        <v>-0.68655305061409877</v>
       </c>
       <c r="G71">
         <v>2.15</v>
       </c>
       <c r="H71">
-        <v>-0.578308966494173</v>
+        <v>-0.57830896649417296</v>
       </c>
       <c r="I71">
-        <v>422.3240051269531</v>
+        <v>422.32400512695312</v>
       </c>
       <c r="J71">
-        <v>412.0715026855469</v>
+        <v>412.07150268554688</v>
       </c>
       <c r="K71">
-        <v>389.2098016357422</v>
+        <v>389.20980163574222</v>
       </c>
       <c r="L71">
-        <v>297.9106006622314</v>
+        <v>297.91060066223139</v>
       </c>
       <c r="M71">
         <v>1.02</v>
       </c>
       <c r="N71">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="P71">
         <v>1</v>
@@ -8925,7 +8948,7 @@
         <v>0</v>
       </c>
       <c r="T71">
-        <v>6.111111111111111</v>
+        <v>6.1111111111111107</v>
       </c>
       <c r="U71" t="b">
         <v>0</v>
@@ -8958,7 +8981,7 @@
         <v>14.3</v>
       </c>
       <c r="AE71">
-        <v>-8.470000000000001</v>
+        <v>-8.4700000000000006</v>
       </c>
       <c r="AF71">
         <v>20.98</v>
@@ -8984,7 +9007,7 @@
         <v>107</v>
       </c>
       <c r="B72">
-        <v>92.48029108550637</v>
+        <v>92.480291085506366</v>
       </c>
       <c r="C72">
         <v>4094</v>
@@ -8996,13 +9019,13 @@
         <v>1.59</v>
       </c>
       <c r="F72">
-        <v>-0.9670470260788406</v>
+        <v>-0.96704702607884063</v>
       </c>
       <c r="G72">
         <v>1.83</v>
       </c>
       <c r="H72">
-        <v>-0.8319602616346715</v>
+        <v>-0.83196026163467152</v>
       </c>
       <c r="I72">
         <v>106.1559997558594</v>
@@ -9011,16 +9034,16 @@
         <v>103.611499786377</v>
       </c>
       <c r="K72">
-        <v>95.50919998168945</v>
+        <v>95.509199981689449</v>
       </c>
       <c r="L72">
-        <v>81.57729969024658</v>
+        <v>81.577299690246576</v>
       </c>
       <c r="M72">
         <v>1.02</v>
       </c>
       <c r="N72">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="P72">
         <v>0</v>
@@ -9086,7 +9109,7 @@
         <v>247</v>
       </c>
       <c r="AK72">
-        <v>23.71738509936283</v>
+        <v>23.717385099362829</v>
       </c>
     </row>
     <row r="73" spans="1:37">
@@ -9094,7 +9117,7 @@
         <v>108</v>
       </c>
       <c r="B73">
-        <v>94.08732565191025</v>
+        <v>94.087325651910248</v>
       </c>
       <c r="C73">
         <v>2390</v>
@@ -9106,16 +9129,16 @@
         <v>1.96</v>
       </c>
       <c r="F73">
-        <v>-0.791144024516206</v>
+        <v>-0.79114402451620602</v>
       </c>
       <c r="G73">
         <v>1.73</v>
       </c>
       <c r="H73">
-        <v>-0.9112262913660774</v>
+        <v>-0.91122629136607736</v>
       </c>
       <c r="I73">
-        <v>118.5199996948242</v>
+        <v>118.51999969482419</v>
       </c>
       <c r="J73">
         <v>117.0385002136231</v>
@@ -9124,13 +9147,13 @@
         <v>106.1425999450684</v>
       </c>
       <c r="L73">
-        <v>86.28339988708495</v>
+        <v>86.283399887084954</v>
       </c>
       <c r="M73">
         <v>1.01</v>
       </c>
       <c r="N73">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="P73">
         <v>1</v>
@@ -9145,7 +9168,7 @@
         <v>0</v>
       </c>
       <c r="T73">
-        <v>6.111111111111111</v>
+        <v>6.1111111111111107</v>
       </c>
       <c r="U73" t="b">
         <v>1</v>
@@ -9163,7 +9186,7 @@
         <v>122.53</v>
       </c>
       <c r="Z73">
-        <v>9.449999999999999</v>
+        <v>9.4499999999999993</v>
       </c>
       <c r="AA73">
         <v>9.17</v>
@@ -9196,7 +9219,7 @@
         <v>245</v>
       </c>
       <c r="AK73">
-        <v>23.65439539754974</v>
+        <v>23.654395397549742</v>
       </c>
     </row>
     <row r="74" spans="1:37">
@@ -9204,7 +9227,7 @@
         <v>109</v>
       </c>
       <c r="B74">
-        <v>97.96846573681019</v>
+        <v>97.968465736810188</v>
       </c>
       <c r="C74">
         <v>2942</v>
@@ -9216,28 +9239,28 @@
         <v>6.37</v>
       </c>
       <c r="F74">
-        <v>1.305429588703306</v>
+        <v>1.3054295887033061</v>
       </c>
       <c r="G74">
         <v>4.5</v>
       </c>
       <c r="H74">
-        <v>1.284442732193864</v>
+        <v>1.2844427321938641</v>
       </c>
       <c r="I74">
-        <v>26.97400016784668</v>
+        <v>26.974000167846679</v>
       </c>
       <c r="J74">
         <v>24.70750007629395</v>
       </c>
       <c r="K74">
-        <v>19.83740007400513</v>
+        <v>19.837400074005132</v>
       </c>
       <c r="L74">
-        <v>16.08174998283386</v>
+        <v>16.081749982833859</v>
       </c>
       <c r="M74">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="N74">
         <v>1.36</v>
@@ -9255,7 +9278,7 @@
         <v>0</v>
       </c>
       <c r="T74">
-        <v>1.111111111111111</v>
+        <v>1.1111111111111109</v>
       </c>
       <c r="U74" t="b">
         <v>0</v>
@@ -9279,7 +9302,7 @@
         <v>-2.11</v>
       </c>
       <c r="AB74">
-        <v>40.34</v>
+        <v>40.340000000000003</v>
       </c>
       <c r="AC74">
         <v>32.54</v>
@@ -9314,7 +9337,7 @@
         <v>110</v>
       </c>
       <c r="B75">
-        <v>92.43480897513645</v>
+        <v>92.434808975136448</v>
       </c>
       <c r="C75">
         <v>142</v>
@@ -9323,28 +9346,28 @@
         <v>194.4</v>
       </c>
       <c r="E75">
-        <v>2.22</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="F75">
-        <v>-0.6675365099046248</v>
+        <v>-0.66753650990462476</v>
       </c>
       <c r="G75">
-        <v>2.55</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="H75">
-        <v>-0.2612448475685497</v>
+        <v>-0.26124484756854971</v>
       </c>
       <c r="I75">
-        <v>185.8339996337891</v>
+        <v>185.83399963378909</v>
       </c>
       <c r="J75">
         <v>190.2959999084473</v>
       </c>
       <c r="K75">
-        <v>189.4391995239258</v>
+        <v>189.43919952392579</v>
       </c>
       <c r="L75">
-        <v>163.9715497207642</v>
+        <v>163.97154972076419</v>
       </c>
       <c r="M75">
         <v>0.98</v>
@@ -9383,7 +9406,7 @@
         <v>212.6</v>
       </c>
       <c r="Z75">
-        <v>1070.14</v>
+        <v>1070.1400000000001</v>
       </c>
       <c r="AA75">
         <v>18.23</v>
@@ -9416,7 +9439,7 @@
         <v>235</v>
       </c>
       <c r="AK75">
-        <v>23.2362121315264</v>
+        <v>23.236212131526401</v>
       </c>
     </row>
     <row r="76" spans="1:37">
@@ -9424,7 +9447,7 @@
         <v>111</v>
       </c>
       <c r="B76">
-        <v>90.17586416009703</v>
+        <v>90.175864160097035</v>
       </c>
       <c r="C76">
         <v>941</v>
@@ -9442,22 +9465,22 @@
         <v>2.5</v>
       </c>
       <c r="H76">
-        <v>-0.3008778624342525</v>
+        <v>-0.30087786243425252</v>
       </c>
       <c r="I76">
-        <v>196.1060028076172</v>
+        <v>196.10600280761719</v>
       </c>
       <c r="J76">
-        <v>180.3455001831055</v>
+        <v>180.34550018310549</v>
       </c>
       <c r="K76">
-        <v>168.0437997436524</v>
+        <v>168.04379974365239</v>
       </c>
       <c r="L76">
-        <v>156.5004750823975</v>
+        <v>156.50047508239749</v>
       </c>
       <c r="M76">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="N76">
         <v>1.17</v>
@@ -9475,7 +9498,7 @@
         <v>2</v>
       </c>
       <c r="T76">
-        <v>3.888888888888889</v>
+        <v>3.8888888888888888</v>
       </c>
       <c r="U76" t="b">
         <v>0</v>
@@ -9502,7 +9525,7 @@
         <v>14.43</v>
       </c>
       <c r="AC76">
-        <v>39.52</v>
+        <v>39.520000000000003</v>
       </c>
       <c r="AD76">
         <v>43.57</v>
@@ -9514,7 +9537,7 @@
         <v>-7.35</v>
       </c>
       <c r="AG76">
-        <v>-67.73999999999999</v>
+        <v>-67.739999999999995</v>
       </c>
       <c r="AH76" t="s">
         <v>168</v>
@@ -9526,7 +9549,7 @@
         <v>249</v>
       </c>
       <c r="AK76">
-        <v>23.15550451725179</v>
+        <v>23.155504517251789</v>
       </c>
     </row>
     <row r="77" spans="1:37">
@@ -9534,7 +9557,7 @@
         <v>112</v>
       </c>
       <c r="B77">
-        <v>98.07459066100667</v>
+        <v>98.074590661006667</v>
       </c>
       <c r="C77">
         <v>1489</v>
@@ -9543,34 +9566,34 @@
         <v>59.23</v>
       </c>
       <c r="E77">
-        <v>2.55</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="F77">
-        <v>-0.5106500490514642</v>
+        <v>-0.51065004905146416</v>
       </c>
       <c r="G77">
-        <v>2.47</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="H77">
-        <v>-0.3246576713536741</v>
+        <v>-0.32465767135367413</v>
       </c>
       <c r="I77">
         <v>56.80399932861328</v>
       </c>
       <c r="J77">
-        <v>55.54649963378906</v>
+        <v>55.546499633789061</v>
       </c>
       <c r="K77">
-        <v>50.90099990844727</v>
+        <v>50.900999908447268</v>
       </c>
       <c r="L77">
-        <v>36.03485005378723</v>
+        <v>36.034850053787231</v>
       </c>
       <c r="M77">
         <v>1.02</v>
       </c>
       <c r="N77">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="P77">
         <v>0</v>
@@ -9636,7 +9659,7 @@
         <v>229</v>
       </c>
       <c r="AK77">
-        <v>23.05464317295253</v>
+        <v>23.054643172952531</v>
       </c>
     </row>
     <row r="78" spans="1:37">
@@ -9644,7 +9667,7 @@
         <v>113</v>
       </c>
       <c r="B78">
-        <v>93.10187992722862</v>
+        <v>93.101879927228623</v>
       </c>
       <c r="C78">
         <v>3027</v>
@@ -9656,7 +9679,7 @@
         <v>4</v>
       </c>
       <c r="F78">
-        <v>0.1786995516669694</v>
+        <v>0.17869955166696941</v>
       </c>
       <c r="G78">
         <v>2.75</v>
@@ -9665,22 +9688,22 @@
         <v>-0.1027127881057379</v>
       </c>
       <c r="I78">
-        <v>309.2640014648438</v>
+        <v>309.26400146484377</v>
       </c>
       <c r="J78">
-        <v>302.8574996948242</v>
+        <v>302.85749969482418</v>
       </c>
       <c r="K78">
-        <v>278.2453994750977</v>
+        <v>278.24539947509771</v>
       </c>
       <c r="L78">
-        <v>226.7888492584229</v>
+        <v>226.78884925842291</v>
       </c>
       <c r="M78">
         <v>1.02</v>
       </c>
       <c r="N78">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="P78">
         <v>0</v>
@@ -9719,7 +9742,7 @@
         <v>-5.22</v>
       </c>
       <c r="AB78">
-        <v>39.95</v>
+        <v>39.950000000000003</v>
       </c>
       <c r="AC78">
         <v>43.04</v>
@@ -9746,7 +9769,7 @@
         <v>217</v>
       </c>
       <c r="AK78">
-        <v>22.98779533655986</v>
+        <v>22.987795336559859</v>
       </c>
     </row>
     <row r="79" spans="1:37">
@@ -9754,7 +9777,7 @@
         <v>114</v>
       </c>
       <c r="B79">
-        <v>90.82777440873257</v>
+        <v>90.827774408732566</v>
       </c>
       <c r="C79">
         <v>3677.5</v>
@@ -9766,13 +9789,13 @@
         <v>2.1</v>
       </c>
       <c r="F79">
-        <v>-0.7245861320330469</v>
+        <v>-0.72458613203304689</v>
       </c>
       <c r="G79">
-        <v>2.24</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="H79">
-        <v>-0.5069695397359075</v>
+        <v>-0.50696953973590753</v>
       </c>
       <c r="I79">
         <v>108.7200012207031</v>
@@ -9781,16 +9804,16 @@
         <v>103.3375007629395</v>
       </c>
       <c r="K79">
-        <v>98.44380004882812</v>
+        <v>98.443800048828123</v>
       </c>
       <c r="L79">
-        <v>88.17799991607666</v>
+        <v>88.177999916076658</v>
       </c>
       <c r="M79">
         <v>1.05</v>
       </c>
       <c r="N79">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="P79">
         <v>0</v>
@@ -9856,7 +9879,7 @@
         <v>214</v>
       </c>
       <c r="AK79">
-        <v>22.95347034015968</v>
+        <v>22.953470340159679</v>
       </c>
     </row>
     <row r="80" spans="1:37">
@@ -9876,31 +9899,31 @@
         <v>3.99</v>
       </c>
       <c r="F80">
-        <v>0.173945416489601</v>
+        <v>0.17394541648960099</v>
       </c>
       <c r="G80">
         <v>2.82</v>
       </c>
       <c r="H80">
-        <v>-0.04722656729375396</v>
+        <v>-4.7226567293753963E-2</v>
       </c>
       <c r="I80">
-        <v>15.27199993133545</v>
+        <v>15.271999931335451</v>
       </c>
       <c r="J80">
         <v>14.57149996757507</v>
       </c>
       <c r="K80">
-        <v>13.71999998092651</v>
+        <v>13.719999980926509</v>
       </c>
       <c r="L80">
-        <v>11.76214999198914</v>
+        <v>11.762149991989141</v>
       </c>
       <c r="M80">
         <v>1.05</v>
       </c>
       <c r="N80">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="P80">
         <v>0</v>
@@ -9936,7 +9959,7 @@
         <v>3.07</v>
       </c>
       <c r="AA80">
-        <v>32.16</v>
+        <v>32.159999999999997</v>
       </c>
       <c r="AB80">
         <v>7.87</v>
@@ -9966,7 +9989,7 @@
         <v>250</v>
       </c>
       <c r="AK80">
-        <v>22.64518630171544</v>
+        <v>22.645186301715441</v>
       </c>
     </row>
     <row r="81" spans="1:37">
@@ -9974,7 +9997,7 @@
         <v>116</v>
       </c>
       <c r="B81">
-        <v>90.66100667070953</v>
+        <v>90.661006670709526</v>
       </c>
       <c r="C81">
         <v>624</v>
@@ -9986,25 +10009,25 @@
         <v>2.57</v>
       </c>
       <c r="F81">
-        <v>-0.5011417786967272</v>
+        <v>-0.50114177869672716</v>
       </c>
       <c r="G81">
         <v>3.65</v>
       </c>
       <c r="H81">
-        <v>0.6106814794769145</v>
+        <v>0.61068147947691453</v>
       </c>
       <c r="I81">
-        <v>64.22600021362305</v>
+        <v>64.226000213623053</v>
       </c>
       <c r="J81">
-        <v>64.38099994659424</v>
+        <v>64.380999946594244</v>
       </c>
       <c r="K81">
-        <v>62.66379981994629</v>
+        <v>62.663799819946291</v>
       </c>
       <c r="L81">
-        <v>51.22749990463257</v>
+        <v>51.227499904632573</v>
       </c>
       <c r="M81">
         <v>1</v>
@@ -10084,13 +10107,13 @@
         <v>117</v>
       </c>
       <c r="B82">
-        <v>98.18071558520315</v>
+        <v>98.180715585203146</v>
       </c>
       <c r="C82">
         <v>1134</v>
       </c>
       <c r="D82">
-        <v>150.92</v>
+        <v>150.91999999999999</v>
       </c>
       <c r="E82">
         <v>1.79</v>
@@ -10102,19 +10125,19 @@
         <v>1.74</v>
       </c>
       <c r="H82">
-        <v>-0.9032996883929368</v>
+        <v>-0.90329968839293684</v>
       </c>
       <c r="I82">
-        <v>151.7319976806641</v>
+        <v>151.73199768066411</v>
       </c>
       <c r="J82">
-        <v>144.7844985961914</v>
+        <v>144.78449859619141</v>
       </c>
       <c r="K82">
         <v>127.1667997741699</v>
       </c>
       <c r="L82">
-        <v>90.90074996948242</v>
+        <v>90.900749969482419</v>
       </c>
       <c r="M82">
         <v>1.05</v>
@@ -10150,7 +10173,7 @@
         <v>43.11</v>
       </c>
       <c r="Y82">
-        <v>155.64</v>
+        <v>155.63999999999999</v>
       </c>
       <c r="Z82">
         <v>13.14</v>
@@ -10186,7 +10209,7 @@
         <v>251</v>
       </c>
       <c r="AK82">
-        <v>21.78607141376746</v>
+        <v>21.786071413767459</v>
       </c>
     </row>
     <row r="83" spans="1:37">
@@ -10194,7 +10217,7 @@
         <v>118</v>
       </c>
       <c r="B83">
-        <v>93.08671922377198</v>
+        <v>93.086719223771979</v>
       </c>
       <c r="C83">
         <v>3170</v>
@@ -10203,28 +10226,28 @@
         <v>176.45</v>
       </c>
       <c r="E83">
-        <v>2.32</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="F83">
-        <v>-0.6199951581309399</v>
+        <v>-0.61999515813093986</v>
       </c>
       <c r="G83">
         <v>2.31</v>
       </c>
       <c r="H83">
-        <v>-0.4514833189239235</v>
+        <v>-0.45148331892392352</v>
       </c>
       <c r="I83">
-        <v>177.6859985351562</v>
+        <v>177.68599853515619</v>
       </c>
       <c r="J83">
-        <v>168.2930000305176</v>
+        <v>168.29300003051759</v>
       </c>
       <c r="K83">
-        <v>163.8383999633789</v>
+        <v>163.83839996337889</v>
       </c>
       <c r="L83">
-        <v>142.7800002670288</v>
+        <v>142.78000026702881</v>
       </c>
       <c r="M83">
         <v>1.06</v>
@@ -10257,7 +10280,7 @@
         <v>0</v>
       </c>
       <c r="X83">
-        <v>84.73999999999999</v>
+        <v>84.74</v>
       </c>
       <c r="Y83">
         <v>183.83</v>
@@ -10296,7 +10319,7 @@
         <v>236</v>
       </c>
       <c r="AK83">
-        <v>21.58827740785704</v>
+        <v>21.588277407857039</v>
       </c>
     </row>
     <row r="84" spans="1:37">
@@ -10304,7 +10327,7 @@
         <v>119</v>
       </c>
       <c r="B84">
-        <v>94.75439660400242</v>
+        <v>94.754396604002423</v>
       </c>
       <c r="C84">
         <v>1108</v>
@@ -10313,28 +10336,28 @@
         <v>246.41</v>
       </c>
       <c r="E84">
-        <v>2.2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F84">
-        <v>-0.6770447802593618</v>
+        <v>-0.67704478025936177</v>
       </c>
       <c r="G84">
         <v>1.91</v>
       </c>
       <c r="H84">
-        <v>-0.7685474378495469</v>
+        <v>-0.76854743784954693</v>
       </c>
       <c r="I84">
         <v>243.3959991455078</v>
       </c>
       <c r="J84">
-        <v>232.8460006713867</v>
+        <v>232.84600067138669</v>
       </c>
       <c r="K84">
-        <v>208.2938009643555</v>
+        <v>208.29380096435551</v>
       </c>
       <c r="L84">
-        <v>162.3579000473023</v>
+        <v>162.35790004730231</v>
       </c>
       <c r="M84">
         <v>1.05</v>
@@ -10391,7 +10414,7 @@
         <v>27.11</v>
       </c>
       <c r="AF84">
-        <v>137.14</v>
+        <v>137.13999999999999</v>
       </c>
       <c r="AG84">
         <v>28.44</v>
@@ -10406,7 +10429,7 @@
         <v>237</v>
       </c>
       <c r="AK84">
-        <v>21.45763273017051</v>
+        <v>21.457632730170509</v>
       </c>
     </row>
     <row r="85" spans="1:37">
@@ -10414,7 +10437,7 @@
         <v>120</v>
       </c>
       <c r="B85">
-        <v>90.94906003638569</v>
+        <v>90.949060036385688</v>
       </c>
       <c r="C85">
         <v>2029</v>
@@ -10426,7 +10449,7 @@
         <v>2.8</v>
       </c>
       <c r="F85">
-        <v>-0.3917966696172515</v>
+        <v>-0.39179666961725151</v>
       </c>
       <c r="G85">
         <v>2.75</v>
@@ -10435,13 +10458,13 @@
         <v>-0.1027127881057379</v>
       </c>
       <c r="I85">
-        <v>34.84199981689453</v>
+        <v>34.841999816894528</v>
       </c>
       <c r="J85">
-        <v>34.97150030136108</v>
+        <v>34.971500301361083</v>
       </c>
       <c r="K85">
-        <v>31.3906001663208</v>
+        <v>31.390600166320802</v>
       </c>
       <c r="L85">
         <v>26.22740006446838</v>
@@ -10450,7 +10473,7 @@
         <v>1</v>
       </c>
       <c r="N85">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="P85">
         <v>1</v>
@@ -10465,7 +10488,7 @@
         <v>0</v>
       </c>
       <c r="T85">
-        <v>2.777777777777778</v>
+        <v>2.7777777777777781</v>
       </c>
       <c r="U85" t="b">
         <v>0</v>
@@ -10477,7 +10500,7 @@
         <v>0</v>
       </c>
       <c r="X85">
-        <v>18.24</v>
+        <v>18.239999999999998</v>
       </c>
       <c r="Y85">
         <v>37.99</v>
@@ -10492,7 +10515,7 @@
         <v>24.51</v>
       </c>
       <c r="AC85">
-        <v>19.9</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="AD85">
         <v>8.4</v>
@@ -10516,7 +10539,7 @@
         <v>231</v>
       </c>
       <c r="AK85">
-        <v>21.3232564764088</v>
+        <v>21.323256476408801</v>
       </c>
     </row>
     <row r="86" spans="1:37">
@@ -10524,7 +10547,7 @@
         <v>121</v>
       </c>
       <c r="B86">
-        <v>90.87325651910248</v>
+        <v>90.873256519102483</v>
       </c>
       <c r="C86">
         <v>267</v>
@@ -10536,25 +10559,25 @@
         <v>2.8</v>
       </c>
       <c r="F86">
-        <v>-0.3917966696172515</v>
+        <v>-0.39179666961725151</v>
       </c>
       <c r="G86">
-        <v>2.26</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="H86">
-        <v>-0.4911163337896267</v>
+        <v>-0.49111633378962671</v>
       </c>
       <c r="I86">
         <v>101.3130004882812</v>
       </c>
       <c r="J86">
-        <v>99.63175048828126</v>
+        <v>99.631750488281256</v>
       </c>
       <c r="K86">
-        <v>99.20955047607421</v>
+        <v>99.209550476074213</v>
       </c>
       <c r="L86">
-        <v>83.42412519454956</v>
+        <v>83.424125194549561</v>
       </c>
       <c r="M86">
         <v>1.02</v>
@@ -10575,7 +10598,7 @@
         <v>0</v>
       </c>
       <c r="T86">
-        <v>0.5555555555555555</v>
+        <v>0.55555555555555547</v>
       </c>
       <c r="U86" t="b">
         <v>0</v>
@@ -10602,7 +10625,7 @@
         <v>26.28</v>
       </c>
       <c r="AC86">
-        <v>35.95</v>
+        <v>35.950000000000003</v>
       </c>
       <c r="AD86">
         <v>33.83</v>
@@ -10626,7 +10649,7 @@
         <v>252</v>
       </c>
       <c r="AK86">
-        <v>21.27665351762444</v>
+        <v>21.276653517624439</v>
       </c>
     </row>
     <row r="87" spans="1:37">
@@ -10634,7 +10657,7 @@
         <v>122</v>
       </c>
       <c r="B87">
-        <v>93.87507580351728</v>
+        <v>93.875075803517277</v>
       </c>
       <c r="C87">
         <v>2093</v>
@@ -10652,25 +10675,25 @@
         <v>2.31</v>
       </c>
       <c r="H87">
-        <v>-0.4514833189239235</v>
+        <v>-0.45148331892392352</v>
       </c>
       <c r="I87">
-        <v>70.88600006103516</v>
+        <v>70.886000061035162</v>
       </c>
       <c r="J87">
-        <v>66.38799953460693</v>
+        <v>66.387999534606934</v>
       </c>
       <c r="K87">
-        <v>61.41539993286133</v>
+        <v>61.415399932861327</v>
       </c>
       <c r="L87">
-        <v>51.36949989318848</v>
+        <v>51.369499893188483</v>
       </c>
       <c r="M87">
         <v>1.07</v>
       </c>
       <c r="N87">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="P87">
         <v>0</v>
@@ -10709,7 +10732,7 @@
         <v>28.17</v>
       </c>
       <c r="AB87">
-        <v>17.31</v>
+        <v>17.309999999999999</v>
       </c>
       <c r="AC87">
         <v>61.5</v>
@@ -10744,7 +10767,7 @@
         <v>123</v>
       </c>
       <c r="B88">
-        <v>90.60036385688296</v>
+        <v>90.600363856882964</v>
       </c>
       <c r="C88">
         <v>205</v>
@@ -10756,22 +10779,22 @@
         <v>2</v>
       </c>
       <c r="F88">
-        <v>-0.772127483806732</v>
+        <v>-0.77212748380673202</v>
       </c>
       <c r="G88">
         <v>1.98</v>
       </c>
       <c r="H88">
-        <v>-0.7130612170375629</v>
+        <v>-0.71306121703756287</v>
       </c>
       <c r="I88">
         <v>13.31199989318848</v>
       </c>
       <c r="J88">
-        <v>13.19499998092651</v>
+        <v>13.194999980926511</v>
       </c>
       <c r="K88">
-        <v>12.69480001449585</v>
+        <v>12.694800014495851</v>
       </c>
       <c r="L88">
         <v>11.11670000314713</v>
@@ -10822,7 +10845,7 @@
         <v>30.41</v>
       </c>
       <c r="AC88">
-        <v>32.63</v>
+        <v>32.630000000000003</v>
       </c>
       <c r="AD88">
         <v>7.31</v>
@@ -10854,43 +10877,43 @@
         <v>124</v>
       </c>
       <c r="B89">
-        <v>92.22255912674349</v>
+        <v>92.222559126743491</v>
       </c>
       <c r="C89">
         <v>1360</v>
       </c>
       <c r="D89">
-        <v>68.93000000000001</v>
+        <v>68.930000000000007</v>
       </c>
       <c r="E89">
         <v>3.49</v>
       </c>
       <c r="F89">
-        <v>-0.06376134237882433</v>
+        <v>-6.3761342378824332E-2</v>
       </c>
       <c r="G89">
         <v>2.46</v>
       </c>
       <c r="H89">
-        <v>-0.3325842743268149</v>
+        <v>-0.33258427432681492</v>
       </c>
       <c r="I89">
-        <v>70.23600006103516</v>
+        <v>70.236000061035156</v>
       </c>
       <c r="J89">
-        <v>67.46950016021728</v>
+        <v>67.469500160217279</v>
       </c>
       <c r="K89">
-        <v>64.4988003540039</v>
+        <v>64.498800354003905</v>
       </c>
       <c r="L89">
-        <v>50.07440015792847</v>
+        <v>50.074400157928473</v>
       </c>
       <c r="M89">
         <v>1.04</v>
       </c>
       <c r="N89">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="P89">
         <v>0</v>
@@ -10956,7 +10979,7 @@
         <v>253</v>
       </c>
       <c r="AK89">
-        <v>20.68151965610823</v>
+        <v>20.681519656108229</v>
       </c>
     </row>
     <row r="90" spans="1:37">
@@ -10964,7 +10987,7 @@
         <v>125</v>
       </c>
       <c r="B90">
-        <v>92.13159490600363</v>
+        <v>92.131594906003627</v>
       </c>
       <c r="C90">
         <v>3103</v>
@@ -10976,22 +10999,22 @@
         <v>2.42</v>
       </c>
       <c r="F90">
-        <v>-0.5724538063572547</v>
+        <v>-0.57245380635725474</v>
       </c>
       <c r="G90">
         <v>1.74</v>
       </c>
       <c r="H90">
-        <v>-0.9032996883929368</v>
+        <v>-0.90329968839293684</v>
       </c>
       <c r="I90">
-        <v>195.4540008544922</v>
+        <v>195.45400085449219</v>
       </c>
       <c r="J90">
         <v>193.2294998168945</v>
       </c>
       <c r="K90">
-        <v>182.0317001342773</v>
+        <v>182.03170013427729</v>
       </c>
       <c r="L90">
         <v>139.8039748764038</v>
@@ -11054,7 +11077,7 @@
         <v>17.32</v>
       </c>
       <c r="AG90">
-        <v>144.23</v>
+        <v>144.22999999999999</v>
       </c>
       <c r="AH90" t="s">
         <v>194</v>
@@ -11066,7 +11089,7 @@
         <v>253</v>
       </c>
       <c r="AK90">
-        <v>20.63560371823395</v>
+        <v>20.635603718233948</v>
       </c>
     </row>
     <row r="91" spans="1:37">
@@ -11074,7 +11097,7 @@
         <v>126</v>
       </c>
       <c r="B91">
-        <v>90.75197089144936</v>
+        <v>90.751970891449361</v>
       </c>
       <c r="C91">
         <v>1784</v>
@@ -11086,25 +11109,25 @@
         <v>1.72</v>
       </c>
       <c r="F91">
-        <v>-0.9052432687730503</v>
+        <v>-0.90524326877305028</v>
       </c>
       <c r="G91">
         <v>1.81</v>
       </c>
       <c r="H91">
-        <v>-0.8478134675809527</v>
+        <v>-0.84781346758095266</v>
       </c>
       <c r="I91">
         <v>15.51400012969971</v>
       </c>
       <c r="J91">
-        <v>15.26950001716614</v>
+        <v>15.269500017166139</v>
       </c>
       <c r="K91">
         <v>15.1506000328064</v>
       </c>
       <c r="L91">
-        <v>12.24145001411438</v>
+        <v>12.241450014114379</v>
       </c>
       <c r="M91">
         <v>1.02</v>
@@ -11137,22 +11160,22 @@
         <v>1</v>
       </c>
       <c r="X91">
-        <v>8.119999999999999</v>
+        <v>8.1199999999999992</v>
       </c>
       <c r="Y91">
-        <v>16.1</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="Z91">
         <v>3.26</v>
       </c>
       <c r="AA91">
-        <v>-17.83</v>
+        <v>-17.829999999999998</v>
       </c>
       <c r="AB91">
         <v>10.67</v>
       </c>
       <c r="AC91">
-        <v>80.31999999999999</v>
+        <v>80.319999999999993</v>
       </c>
       <c r="AD91">
         <v>4.38</v>
@@ -11164,7 +11187,7 @@
         <v>188.89</v>
       </c>
       <c r="AG91">
-        <v>-142.86</v>
+        <v>-142.86000000000001</v>
       </c>
       <c r="AH91" t="s">
         <v>179</v>
@@ -11176,7 +11199,7 @@
         <v>250</v>
       </c>
       <c r="AK91">
-        <v>20.26839731654091</v>
+        <v>20.268397316540909</v>
       </c>
     </row>
     <row r="92" spans="1:37">
@@ -11184,37 +11207,37 @@
         <v>127</v>
       </c>
       <c r="B92">
-        <v>91.93450576106731</v>
+        <v>91.934505761067314</v>
       </c>
       <c r="C92">
         <v>4794</v>
       </c>
       <c r="D92">
-        <v>75.68000000000001</v>
+        <v>75.680000000000007</v>
       </c>
       <c r="E92">
         <v>2.62</v>
       </c>
       <c r="F92">
-        <v>-0.4773711028098845</v>
+        <v>-0.47737110280988448</v>
       </c>
       <c r="G92">
-        <v>2.45</v>
+        <v>2.4500000000000002</v>
       </c>
       <c r="H92">
-        <v>-0.3405108772999553</v>
+        <v>-0.34051087729995527</v>
       </c>
       <c r="I92">
         <v>76.94900207519531</v>
       </c>
       <c r="J92">
-        <v>73.07875118255615</v>
+        <v>73.078751182556147</v>
       </c>
       <c r="K92">
         <v>63.39220062255859</v>
       </c>
       <c r="L92">
-        <v>49.07520017623902</v>
+        <v>49.075200176239022</v>
       </c>
       <c r="M92">
         <v>1.05</v>
@@ -11286,7 +11309,7 @@
         <v>229</v>
       </c>
       <c r="AK92">
-        <v>20.22688269994165</v>
+        <v>20.226882699941651</v>
       </c>
     </row>
     <row r="93" spans="1:37">
@@ -11306,25 +11329,25 @@
         <v>4.47</v>
       </c>
       <c r="F93">
-        <v>0.4021439050032892</v>
+        <v>0.40214390500328923</v>
       </c>
       <c r="G93">
         <v>3.07</v>
       </c>
       <c r="H93">
-        <v>0.1509385070347606</v>
+        <v>0.15093850703476061</v>
       </c>
       <c r="I93">
-        <v>67.22599945068359</v>
+        <v>67.225999450683588</v>
       </c>
       <c r="J93">
-        <v>64.64500026702881</v>
+        <v>64.645000267028806</v>
       </c>
       <c r="K93">
-        <v>57.59660026550293</v>
+        <v>57.596600265502929</v>
       </c>
       <c r="L93">
-        <v>48.10360006332397</v>
+        <v>48.103600063323967</v>
       </c>
       <c r="M93">
         <v>1.04</v>
@@ -11396,7 +11419,7 @@
         <v>227</v>
       </c>
       <c r="AK93">
-        <v>20.13133503662099</v>
+        <v>20.131335036620989</v>
       </c>
     </row>
     <row r="94" spans="1:37">
@@ -11404,7 +11427,7 @@
         <v>129</v>
       </c>
       <c r="B94">
-        <v>96.40691328077622</v>
+        <v>96.406913280776223</v>
       </c>
       <c r="C94">
         <v>3834.5</v>
@@ -11416,25 +11439,25 @@
         <v>2.5</v>
       </c>
       <c r="F94">
-        <v>-0.5344207249383066</v>
+        <v>-0.53442072493830661</v>
       </c>
       <c r="G94">
         <v>2.15</v>
       </c>
       <c r="H94">
-        <v>-0.578308966494173</v>
+        <v>-0.57830896649417296</v>
       </c>
       <c r="I94">
         <v>61.52200012207031</v>
       </c>
       <c r="J94">
-        <v>57.32100009918213</v>
+        <v>57.321000099182129</v>
       </c>
       <c r="K94">
-        <v>49.01640014648437</v>
+        <v>49.016400146484372</v>
       </c>
       <c r="L94">
-        <v>36.77635009765625</v>
+        <v>36.776350097656248</v>
       </c>
       <c r="M94">
         <v>1.07</v>
@@ -11455,7 +11478,7 @@
         <v>0</v>
       </c>
       <c r="T94">
-        <v>1.111111111111111</v>
+        <v>1.1111111111111109</v>
       </c>
       <c r="U94" t="b">
         <v>1</v>
@@ -11494,7 +11517,7 @@
         <v>8.82</v>
       </c>
       <c r="AG94">
-        <v>17.24</v>
+        <v>17.239999999999998</v>
       </c>
       <c r="AH94" t="s">
         <v>163</v>
@@ -11523,34 +11546,34 @@
         <v>180.11</v>
       </c>
       <c r="E95">
-        <v>4.86</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="F95">
-        <v>0.5875551769206612</v>
+        <v>0.58755517692066117</v>
       </c>
       <c r="G95">
         <v>3.32</v>
       </c>
       <c r="H95">
-        <v>0.3491035813632752</v>
+        <v>0.34910358136327518</v>
       </c>
       <c r="I95">
         <v>182.0779968261719</v>
       </c>
       <c r="J95">
-        <v>175.0239997863769</v>
+        <v>175.02399978637689</v>
       </c>
       <c r="K95">
-        <v>156.6167993164063</v>
+        <v>156.61679931640629</v>
       </c>
       <c r="L95">
-        <v>135.0981496047974</v>
+        <v>135.09814960479741</v>
       </c>
       <c r="M95">
         <v>1.04</v>
       </c>
       <c r="N95">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="P95">
         <v>0</v>
@@ -11595,7 +11618,7 @@
         <v>28.39</v>
       </c>
       <c r="AD95">
-        <v>20.17</v>
+        <v>20.170000000000002</v>
       </c>
       <c r="AE95">
         <v>-39.11</v>
@@ -11616,7 +11639,7 @@
         <v>227</v>
       </c>
       <c r="AK95">
-        <v>19.68774982154529</v>
+        <v>19.687749821545289</v>
       </c>
     </row>
     <row r="96" spans="1:37">
@@ -11624,7 +11647,7 @@
         <v>131</v>
       </c>
       <c r="B96">
-        <v>93.32929047907822</v>
+        <v>93.329290479078225</v>
       </c>
       <c r="C96">
         <v>5105</v>
@@ -11636,31 +11659,31 @@
         <v>3.76</v>
       </c>
       <c r="F96">
-        <v>0.06460030741012517</v>
+        <v>6.4600307410125166E-2</v>
       </c>
       <c r="G96">
         <v>3.21</v>
       </c>
       <c r="H96">
-        <v>0.2619109486587289</v>
+        <v>0.26191094865872888</v>
       </c>
       <c r="I96">
         <v>51.58999938964844</v>
       </c>
       <c r="J96">
-        <v>49.88949966430664</v>
+        <v>49.889499664306641</v>
       </c>
       <c r="K96">
-        <v>45.80519981384278</v>
+        <v>45.805199813842783</v>
       </c>
       <c r="L96">
-        <v>41.26129998207092</v>
+        <v>41.261299982070923</v>
       </c>
       <c r="M96">
         <v>1.03</v>
       </c>
       <c r="N96">
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="P96">
         <v>0</v>
@@ -11734,7 +11757,7 @@
         <v>132</v>
       </c>
       <c r="B97">
-        <v>90.63068526379624</v>
+        <v>90.630685263796238</v>
       </c>
       <c r="C97">
         <v>3062</v>
@@ -11746,7 +11769,7 @@
         <v>3.61</v>
       </c>
       <c r="F97">
-        <v>-0.006711720250402405</v>
+        <v>-6.7117202504024054E-3</v>
       </c>
       <c r="G97">
         <v>2.58</v>
@@ -11755,16 +11778,16 @@
         <v>-0.2374650386491278</v>
       </c>
       <c r="I97">
-        <v>93.29199981689453</v>
+        <v>93.291999816894531</v>
       </c>
       <c r="J97">
         <v>89.81949958801269</v>
       </c>
       <c r="K97">
-        <v>86.46579986572266</v>
+        <v>86.465799865722659</v>
       </c>
       <c r="L97">
-        <v>72.41415014266968</v>
+        <v>72.414150142669683</v>
       </c>
       <c r="M97">
         <v>1.04</v>
@@ -11809,7 +11832,7 @@
         <v>-9.01</v>
       </c>
       <c r="AB97">
-        <v>9.630000000000001</v>
+        <v>9.6300000000000008</v>
       </c>
       <c r="AC97">
         <v>65.75</v>
@@ -11844,7 +11867,7 @@
         <v>133</v>
       </c>
       <c r="B98">
-        <v>96.04305639781685</v>
+        <v>96.043056397816855</v>
       </c>
       <c r="C98">
         <v>3619</v>
@@ -11856,13 +11879,13 @@
         <v>2.73</v>
       </c>
       <c r="F98">
-        <v>-0.425075615858831</v>
+        <v>-0.42507561585883102</v>
       </c>
       <c r="G98">
         <v>2.19</v>
       </c>
       <c r="H98">
-        <v>-0.5466025546016106</v>
+        <v>-0.54660255460161056</v>
       </c>
       <c r="I98">
         <v>106.0360000610352</v>
@@ -11871,16 +11894,16 @@
         <v>101.5625003814697</v>
       </c>
       <c r="K98">
-        <v>91.6784001159668</v>
+        <v>91.678400115966795</v>
       </c>
       <c r="L98">
-        <v>73.41080003738404</v>
+        <v>73.410800037384035</v>
       </c>
       <c r="M98">
         <v>1.04</v>
       </c>
       <c r="N98">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="P98">
         <v>0</v>
@@ -11946,7 +11969,7 @@
         <v>227</v>
       </c>
       <c r="AK98">
-        <v>18.96506836968821</v>
+        <v>18.965068369688211</v>
       </c>
     </row>
     <row r="99" spans="1:37">
@@ -11972,25 +11995,25 @@
         <v>2.91</v>
       </c>
       <c r="H99">
-        <v>0.02411285946451153</v>
+        <v>2.411285946451153E-2</v>
       </c>
       <c r="I99">
-        <v>57.56599960327149</v>
+        <v>57.565999603271493</v>
       </c>
       <c r="J99">
-        <v>56.13699970245361</v>
+        <v>56.136999702453608</v>
       </c>
       <c r="K99">
         <v>50.31</v>
       </c>
       <c r="L99">
-        <v>42.76074998855591</v>
+        <v>42.760749988555908</v>
       </c>
       <c r="M99">
         <v>1.03</v>
       </c>
       <c r="N99">
-        <v>1.14</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="P99">
         <v>0</v>
@@ -12044,7 +12067,7 @@
         <v>-120.51</v>
       </c>
       <c r="AG99">
-        <v>85.70999999999999</v>
+        <v>85.71</v>
       </c>
       <c r="AH99" t="s">
         <v>190</v>
@@ -12056,7 +12079,7 @@
         <v>229</v>
       </c>
       <c r="AK99">
-        <v>18.93604064947837</v>
+        <v>18.936040649478372</v>
       </c>
     </row>
     <row r="100" spans="1:37">
@@ -12085,16 +12108,16 @@
         <v>-1.244143616237982</v>
       </c>
       <c r="I100">
-        <v>415.9120056152344</v>
+        <v>415.91200561523442</v>
       </c>
       <c r="J100">
         <v>408.5105010986328</v>
       </c>
       <c r="K100">
-        <v>397.9494006347657</v>
+        <v>397.94940063476571</v>
       </c>
       <c r="L100">
-        <v>340.9156509399414</v>
+        <v>340.91565093994137</v>
       </c>
       <c r="M100">
         <v>1.02</v>
@@ -12133,7 +12156,7 @@
         <v>422</v>
       </c>
       <c r="Z100">
-        <v>85.48999999999999</v>
+        <v>85.49</v>
       </c>
       <c r="AA100">
         <v>10.15</v>
@@ -12174,7 +12197,7 @@
         <v>136</v>
       </c>
       <c r="B101">
-        <v>90.35779260157672</v>
+        <v>90.357792601576719</v>
       </c>
       <c r="C101">
         <v>3356</v>
@@ -12186,13 +12209,13 @@
         <v>3.74</v>
       </c>
       <c r="F101">
-        <v>0.05509203705538835</v>
+        <v>5.509203705538835E-2</v>
       </c>
       <c r="G101">
         <v>2.52</v>
       </c>
       <c r="H101">
-        <v>-0.2850246564879713</v>
+        <v>-0.28502465648797132</v>
       </c>
       <c r="I101">
         <v>166.1040008544922</v>
@@ -12201,7 +12224,7 @@
         <v>159.0314987182617</v>
       </c>
       <c r="K101">
-        <v>147.4915994262695</v>
+        <v>147.49159942626949</v>
       </c>
       <c r="L101">
         <v>117.953699798584</v>
@@ -12210,7 +12233,7 @@
         <v>1.04</v>
       </c>
       <c r="N101">
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="P101">
         <v>0</v>
@@ -12237,7 +12260,7 @@
         <v>1</v>
       </c>
       <c r="X101">
-        <v>88.51000000000001</v>
+        <v>88.51</v>
       </c>
       <c r="Y101">
         <v>168.92</v>
@@ -12284,7 +12307,7 @@
         <v>137</v>
       </c>
       <c r="B102">
-        <v>96.75560946027896</v>
+        <v>96.755609460278961</v>
       </c>
       <c r="C102">
         <v>1827</v>
@@ -12296,28 +12319,28 @@
         <v>6.52</v>
       </c>
       <c r="F102">
-        <v>1.376741616363833</v>
+        <v>1.3767416163638331</v>
       </c>
       <c r="G102">
         <v>3.99</v>
       </c>
       <c r="H102">
-        <v>0.8801859805636946</v>
+        <v>0.88018598056369457</v>
       </c>
       <c r="I102">
-        <v>633.8940063476563</v>
+        <v>633.89400634765627</v>
       </c>
       <c r="J102">
-        <v>583.9170013427735</v>
+        <v>583.91700134277346</v>
       </c>
       <c r="K102">
-        <v>488.2632000732422</v>
+        <v>488.26320007324222</v>
       </c>
       <c r="L102">
-        <v>358.3752006530761</v>
+        <v>358.37520065307609</v>
       </c>
       <c r="M102">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="N102">
         <v>1.3</v>
@@ -12335,7 +12358,7 @@
         <v>0</v>
       </c>
       <c r="T102">
-        <v>2.222222222222222</v>
+        <v>2.2222222222222219</v>
       </c>
       <c r="U102" t="b">
         <v>0</v>
@@ -12371,7 +12394,7 @@
         <v>64.81</v>
       </c>
       <c r="AF102">
-        <v>-69.48999999999999</v>
+        <v>-69.489999999999995</v>
       </c>
       <c r="AG102">
         <v>139.19</v>
@@ -12386,7 +12409,7 @@
         <v>231</v>
       </c>
       <c r="AK102">
-        <v>17.98316583766831</v>
+        <v>17.983165837668309</v>
       </c>
     </row>
     <row r="103" spans="1:37">
@@ -12394,37 +12417,37 @@
         <v>138</v>
       </c>
       <c r="B103">
-        <v>96.64948453608247</v>
+        <v>96.649484536082468</v>
       </c>
       <c r="C103">
         <v>2520</v>
       </c>
       <c r="D103">
-        <v>83.26000000000001</v>
+        <v>83.26</v>
       </c>
       <c r="E103">
         <v>3.63</v>
       </c>
       <c r="F103">
-        <v>0.002796550104334617</v>
+        <v>2.796550104334617E-3</v>
       </c>
       <c r="G103">
-        <v>2.55</v>
+        <v>2.5499999999999998</v>
       </c>
       <c r="H103">
-        <v>-0.2612448475685497</v>
+        <v>-0.26124484756854971</v>
       </c>
       <c r="I103">
-        <v>83.56000061035157</v>
+        <v>83.560000610351565</v>
       </c>
       <c r="J103">
-        <v>79.95449981689453</v>
+        <v>79.954499816894526</v>
       </c>
       <c r="K103">
         <v>68.38020004272461</v>
       </c>
       <c r="L103">
-        <v>53.84239988327026</v>
+        <v>53.842399883270261</v>
       </c>
       <c r="M103">
         <v>1.05</v>
@@ -12481,7 +12504,7 @@
         <v>18.48</v>
       </c>
       <c r="AF103">
-        <v>162.86</v>
+        <v>162.86000000000001</v>
       </c>
       <c r="AG103">
         <v>-51.39</v>
@@ -12496,7 +12519,7 @@
         <v>228</v>
       </c>
       <c r="AK103">
-        <v>17.89166447850017</v>
+        <v>17.891664478500171</v>
       </c>
     </row>
     <row r="104" spans="1:37">
@@ -12516,25 +12539,25 @@
         <v>10.38</v>
       </c>
       <c r="F104">
-        <v>3.211837794828078</v>
+        <v>3.2118377948280781</v>
       </c>
       <c r="G104">
         <v>6.16</v>
       </c>
       <c r="H104">
-        <v>2.600258825735201</v>
+        <v>2.6002588257352008</v>
       </c>
       <c r="I104">
-        <v>6.654000091552734</v>
+        <v>6.6540000915527342</v>
       </c>
       <c r="J104">
-        <v>6.59350004196167</v>
+        <v>6.5935000419616703</v>
       </c>
       <c r="K104">
-        <v>5.582600002288818</v>
+        <v>5.5826000022888183</v>
       </c>
       <c r="L104">
-        <v>4.576525000333786</v>
+        <v>4.5765250003337856</v>
       </c>
       <c r="M104">
         <v>1.01</v>
@@ -12573,16 +12596,16 @@
         <v>7.28</v>
       </c>
       <c r="Z104">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="AA104" t="s">
         <v>157</v>
       </c>
       <c r="AB104">
-        <v>40.38</v>
+        <v>40.380000000000003</v>
       </c>
       <c r="AC104">
-        <v>8.199999999999999</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="AD104">
         <v>8.56</v>
@@ -12594,7 +12617,7 @@
         <v>50</v>
       </c>
       <c r="AG104">
-        <v>-9.710000000000001</v>
+        <v>-9.7100000000000009</v>
       </c>
       <c r="AH104" t="s">
         <v>179</v>
@@ -12606,7 +12629,7 @@
         <v>210</v>
       </c>
       <c r="AK104">
-        <v>16.86615530831646</v>
+        <v>16.866155308316461</v>
       </c>
     </row>
     <row r="105" spans="1:37">
@@ -12626,31 +12649,31 @@
         <v>2.48</v>
       </c>
       <c r="F105">
-        <v>-0.5439289952930437</v>
+        <v>-0.54392899529304373</v>
       </c>
       <c r="G105">
         <v>3.93</v>
       </c>
       <c r="H105">
-        <v>0.832626362724851</v>
+        <v>0.83262636272485102</v>
       </c>
       <c r="I105">
-        <v>173.45400390625</v>
+        <v>173.45400390624999</v>
       </c>
       <c r="J105">
         <v>170.4470008850098</v>
       </c>
       <c r="K105">
-        <v>158.4640005493164</v>
+        <v>158.46400054931641</v>
       </c>
       <c r="L105">
-        <v>128.0517001342774</v>
+        <v>128.05170013427741</v>
       </c>
       <c r="M105">
         <v>1.02</v>
       </c>
       <c r="N105">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="P105">
         <v>0</v>
@@ -12692,7 +12715,7 @@
         <v>15.26</v>
       </c>
       <c r="AC105">
-        <v>19.01</v>
+        <v>19.010000000000002</v>
       </c>
       <c r="AD105">
         <v>77.23</v>
@@ -12716,7 +12739,7 @@
         <v>210</v>
       </c>
       <c r="AK105">
-        <v>16.10504656641711</v>
+        <v>16.105046566417109</v>
       </c>
     </row>
     <row r="106" spans="1:37">
@@ -12724,13 +12747,13 @@
         <v>141</v>
       </c>
       <c r="B106">
-        <v>91.13098847786537</v>
+        <v>91.130988477865372</v>
       </c>
       <c r="C106">
         <v>3495</v>
       </c>
       <c r="D106">
-        <v>159.14</v>
+        <v>159.13999999999999</v>
       </c>
       <c r="E106">
         <v>1.34</v>
@@ -12745,22 +12768,22 @@
         <v>-1.323409645969388</v>
       </c>
       <c r="I106">
-        <v>160.6320007324219</v>
+        <v>160.63200073242189</v>
       </c>
       <c r="J106">
-        <v>155.0440002441406</v>
+        <v>155.04400024414059</v>
       </c>
       <c r="K106">
-        <v>143.7610000610352</v>
+        <v>143.76100006103519</v>
       </c>
       <c r="L106">
-        <v>125.7060502243042</v>
+        <v>125.70605022430421</v>
       </c>
       <c r="M106">
         <v>1.04</v>
       </c>
       <c r="N106">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="P106">
         <v>0</v>
@@ -12775,7 +12798,7 @@
         <v>0</v>
       </c>
       <c r="T106">
-        <v>1.111111111111111</v>
+        <v>1.1111111111111109</v>
       </c>
       <c r="U106" t="b">
         <v>0</v>
@@ -12787,7 +12810,7 @@
         <v>0</v>
       </c>
       <c r="X106">
-        <v>84.54000000000001</v>
+        <v>84.54</v>
       </c>
       <c r="Y106">
         <v>164.4</v>
@@ -12808,7 +12831,7 @@
         <v>38.31</v>
       </c>
       <c r="AE106">
-        <v>17.33</v>
+        <v>17.329999999999998</v>
       </c>
       <c r="AF106">
         <v>9.49</v>
@@ -12826,7 +12849,7 @@
         <v>236</v>
       </c>
       <c r="AK106">
-        <v>16.09099695536411</v>
+        <v>16.090996955364108</v>
       </c>
     </row>
     <row r="107" spans="1:37">
@@ -12834,7 +12857,7 @@
         <v>142</v>
       </c>
       <c r="B107">
-        <v>93.34445118253487</v>
+        <v>93.344451182534868</v>
       </c>
       <c r="C107">
         <v>1759</v>
@@ -12852,25 +12875,25 @@
         <v>1.7</v>
       </c>
       <c r="H107">
-        <v>-0.9350061002854991</v>
+        <v>-0.93500610028549913</v>
       </c>
       <c r="I107">
-        <v>37.19400024414062</v>
+        <v>37.194000244140618</v>
       </c>
       <c r="J107">
-        <v>35.52649965286255</v>
+        <v>35.526499652862547</v>
       </c>
       <c r="K107">
-        <v>33.24109985351563</v>
+        <v>33.241099853515628</v>
       </c>
       <c r="L107">
-        <v>26.24337504386902</v>
+        <v>26.243375043869019</v>
       </c>
       <c r="M107">
         <v>1.05</v>
       </c>
       <c r="N107">
-        <v>1.12</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="P107">
         <v>1</v>
@@ -12885,7 +12908,7 @@
         <v>0</v>
       </c>
       <c r="T107">
-        <v>0.5555555555555555</v>
+        <v>0.55555555555555547</v>
       </c>
       <c r="U107" t="b">
         <v>1</v>
@@ -12900,7 +12923,7 @@
         <v>16.02</v>
       </c>
       <c r="Y107">
-        <v>38.45</v>
+        <v>38.450000000000003</v>
       </c>
       <c r="Z107">
         <v>5.63</v>
@@ -12909,7 +12932,7 @@
         <v>-12.55</v>
       </c>
       <c r="AB107">
-        <v>73.06999999999999</v>
+        <v>73.069999999999993</v>
       </c>
       <c r="AC107">
         <v>2.37</v>
@@ -12918,7 +12941,7 @@
         <v>14.12</v>
       </c>
       <c r="AE107">
-        <v>-8.449999999999999</v>
+        <v>-8.4499999999999993</v>
       </c>
       <c r="AF107">
         <v>20.34</v>
@@ -12944,7 +12967,7 @@
         <v>143</v>
       </c>
       <c r="B108">
-        <v>92.02546998180715</v>
+        <v>92.025469981807149</v>
       </c>
       <c r="C108">
         <v>3632</v>
@@ -12956,31 +12979,31 @@
         <v>2.84</v>
       </c>
       <c r="F108">
-        <v>-0.3727801289077775</v>
+        <v>-0.37278012890777751</v>
       </c>
       <c r="G108">
-        <v>2.26</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="H108">
-        <v>-0.4911163337896267</v>
+        <v>-0.49111633378962671</v>
       </c>
       <c r="I108">
-        <v>93.53000030517578</v>
+        <v>93.530000305175776</v>
       </c>
       <c r="J108">
-        <v>87.48150100708008</v>
+        <v>87.481501007080084</v>
       </c>
       <c r="K108">
-        <v>82.71460067749024</v>
+        <v>82.714600677490239</v>
       </c>
       <c r="L108">
-        <v>78.83900020599366</v>
+        <v>78.839000205993656</v>
       </c>
       <c r="M108">
         <v>1.07</v>
       </c>
       <c r="N108">
-        <v>1.13</v>
+        <v>1.1299999999999999</v>
       </c>
       <c r="P108">
         <v>0</v>
@@ -13013,7 +13036,7 @@
         <v>97.98</v>
       </c>
       <c r="Z108">
-        <v>2.47</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="AA108">
         <v>12.02</v>
@@ -13054,7 +13077,7 @@
         <v>144</v>
       </c>
       <c r="B109">
-        <v>91.96482716798059</v>
+        <v>91.964827167980587</v>
       </c>
       <c r="C109">
         <v>1023</v>
@@ -13066,25 +13089,25 @@
         <v>1.65</v>
       </c>
       <c r="F109">
-        <v>-0.9385222150146298</v>
+        <v>-0.93852221501462985</v>
       </c>
       <c r="G109">
         <v>1.68</v>
       </c>
       <c r="H109">
-        <v>-0.9508593062317804</v>
+        <v>-0.95085930623178039</v>
       </c>
       <c r="I109">
         <v>10.13600006103516</v>
       </c>
       <c r="J109">
-        <v>10.09349994659424</v>
+        <v>10.093499946594241</v>
       </c>
       <c r="K109">
-        <v>9.651800041198731</v>
+        <v>9.6518000411987313</v>
       </c>
       <c r="L109">
-        <v>8.348500018119813</v>
+        <v>8.3485000181198128</v>
       </c>
       <c r="M109">
         <v>1</v>
@@ -13129,7 +13152,7 @@
         <v>25.17</v>
       </c>
       <c r="AB109">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="AC109">
         <v>47.31</v>
@@ -13158,43 +13181,43 @@
         <v>145</v>
       </c>
       <c r="B110">
-        <v>94.02668283808369</v>
+        <v>94.026682838083687</v>
       </c>
       <c r="C110">
         <v>3797</v>
       </c>
       <c r="D110">
-        <v>67.31999999999999</v>
+        <v>67.319999999999993</v>
       </c>
       <c r="E110">
         <v>3.52</v>
       </c>
       <c r="F110">
-        <v>-0.0494989368467189</v>
+        <v>-4.9498936846718897E-2</v>
       </c>
       <c r="G110">
-        <v>2.49</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="H110">
-        <v>-0.3088044654073929</v>
+        <v>-0.30880446540739293</v>
       </c>
       <c r="I110">
-        <v>67.90399932861328</v>
+        <v>67.903999328613281</v>
       </c>
       <c r="J110">
-        <v>66.1325008392334</v>
+        <v>66.132500839233401</v>
       </c>
       <c r="K110">
-        <v>60.9378003692627</v>
+        <v>60.937800369262703</v>
       </c>
       <c r="L110">
-        <v>47.94890001296997</v>
+        <v>47.948900012969972</v>
       </c>
       <c r="M110">
         <v>1.03</v>
       </c>
       <c r="N110">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="P110">
         <v>4</v>
@@ -13236,7 +13259,7 @@
         <v>1.43</v>
       </c>
       <c r="AC110">
-        <v>33.66</v>
+        <v>33.659999999999997</v>
       </c>
       <c r="AD110">
         <v>4.3</v>
@@ -13260,7 +13283,7 @@
         <v>229</v>
       </c>
       <c r="AK110">
-        <v>14.3403587615186</v>
+        <v>14.340358761518599</v>
       </c>
     </row>
     <row r="111" spans="1:37">
@@ -13268,7 +13291,7 @@
         <v>146</v>
       </c>
       <c r="B111">
-        <v>94.42086112795633</v>
+        <v>94.420861127956329</v>
       </c>
       <c r="C111">
         <v>4088</v>
@@ -13280,16 +13303,16 @@
         <v>2.67</v>
       </c>
       <c r="F111">
-        <v>-0.4536004269230421</v>
+        <v>-0.45360042692304209</v>
       </c>
       <c r="G111">
-        <v>2.53</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="H111">
-        <v>-0.2770980535148309</v>
+        <v>-0.27709805351483091</v>
       </c>
       <c r="I111">
-        <v>135.4659973144531</v>
+        <v>135.46599731445309</v>
       </c>
       <c r="J111">
         <v>126.0039993286133</v>
@@ -13298,13 +13321,13 @@
         <v>124.6663995361328</v>
       </c>
       <c r="L111">
-        <v>99.98214981079101</v>
+        <v>99.982149810791014</v>
       </c>
       <c r="M111">
         <v>1.08</v>
       </c>
       <c r="N111">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="P111">
         <v>0</v>
@@ -13319,7 +13342,7 @@
         <v>1</v>
       </c>
       <c r="T111">
-        <v>2.777777777777778</v>
+        <v>2.7777777777777781</v>
       </c>
       <c r="U111" t="b">
         <v>0</v>
@@ -13334,7 +13357,7 @@
         <v>54.44</v>
       </c>
       <c r="Y111">
-        <v>138.86</v>
+        <v>138.86000000000001</v>
       </c>
       <c r="Z111">
         <v>2.63</v>
@@ -13370,7 +13393,7 @@
         <v>259</v>
       </c>
       <c r="AK111">
-        <v>14.22148310036719</v>
+        <v>14.221483100367189</v>
       </c>
     </row>
     <row r="112" spans="1:37">
@@ -13378,7 +13401,7 @@
         <v>147</v>
       </c>
       <c r="B112">
-        <v>90.00909642207398</v>
+        <v>90.009096422073981</v>
       </c>
       <c r="C112">
         <v>1907</v>
@@ -13399,22 +13422,22 @@
         <v>-1.022198732990045</v>
       </c>
       <c r="I112">
-        <v>344.0619995117187</v>
+        <v>344.06199951171868</v>
       </c>
       <c r="J112">
-        <v>330.3205001831055</v>
+        <v>330.32050018310548</v>
       </c>
       <c r="K112">
-        <v>315.6882000732422</v>
+        <v>315.68820007324217</v>
       </c>
       <c r="L112">
-        <v>273.0728004455567</v>
+        <v>273.07280044555671</v>
       </c>
       <c r="M112">
         <v>1.04</v>
       </c>
       <c r="N112">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="P112">
         <v>0</v>
@@ -13488,7 +13511,7 @@
         <v>148</v>
       </c>
       <c r="B113">
-        <v>92.40448756822317</v>
+        <v>92.404487568223175</v>
       </c>
       <c r="C113">
         <v>1960</v>
@@ -13500,25 +13523,25 @@
         <v>2.34</v>
       </c>
       <c r="F113">
-        <v>-0.6104868877762029</v>
+        <v>-0.61048688777620286</v>
       </c>
       <c r="G113">
         <v>1.77</v>
       </c>
       <c r="H113">
-        <v>-0.8795198794735151</v>
+        <v>-0.87951987947351506</v>
       </c>
       <c r="I113">
-        <v>43.55600051879883</v>
+        <v>43.556000518798832</v>
       </c>
       <c r="J113">
-        <v>42.77700004577637</v>
+        <v>42.777000045776369</v>
       </c>
       <c r="K113">
-        <v>40.25839996337891</v>
+        <v>40.258399963378913</v>
       </c>
       <c r="L113">
-        <v>32.65935001373291</v>
+        <v>32.659350013732912</v>
       </c>
       <c r="M113">
         <v>1.02</v>
@@ -13566,10 +13589,10 @@
         <v>5.89</v>
       </c>
       <c r="AC113">
-        <v>16.06</v>
+        <v>16.059999999999999</v>
       </c>
       <c r="AD113">
-        <v>141.08</v>
+        <v>141.08000000000001</v>
       </c>
       <c r="AE113">
         <v>-20.9</v>
@@ -13590,7 +13613,7 @@
         <v>260</v>
       </c>
       <c r="AK113">
-        <v>11.96574774343818</v>
+        <v>11.965747743438181</v>
       </c>
     </row>
     <row r="114" spans="1:37">
@@ -13598,7 +13621,7 @@
         <v>149</v>
       </c>
       <c r="B114">
-        <v>91.38872043662826</v>
+        <v>91.388720436628262</v>
       </c>
       <c r="C114">
         <v>886</v>
@@ -13610,25 +13633,25 @@
         <v>6.45</v>
       </c>
       <c r="F114">
-        <v>1.343462670122254</v>
+        <v>1.3434626701222541</v>
       </c>
       <c r="G114">
-        <v>4.11</v>
+        <v>4.1100000000000003</v>
       </c>
       <c r="H114">
-        <v>0.9753052162413817</v>
+        <v>0.97530521624138167</v>
       </c>
       <c r="I114">
-        <v>174.5280029296875</v>
+        <v>174.52800292968749</v>
       </c>
       <c r="J114">
         <v>148.822501373291</v>
       </c>
       <c r="K114">
-        <v>146.296799621582</v>
+        <v>146.29679962158201</v>
       </c>
       <c r="L114">
-        <v>143.7769498062134</v>
+        <v>143.77694980621339</v>
       </c>
       <c r="M114">
         <v>1.17</v>
@@ -13661,7 +13684,7 @@
         <v>1</v>
       </c>
       <c r="X114">
-        <v>93.70999999999999</v>
+        <v>93.71</v>
       </c>
       <c r="Y114">
         <v>181.42</v>
@@ -13700,7 +13723,7 @@
         <v>261</v>
       </c>
       <c r="AK114">
-        <v>11.92896106539862</v>
+        <v>11.928961065398619</v>
       </c>
     </row>
     <row r="115" spans="1:37">
@@ -13708,7 +13731,7 @@
         <v>150</v>
       </c>
       <c r="B115">
-        <v>91.07034566403881</v>
+        <v>91.070345664038811</v>
       </c>
       <c r="C115">
         <v>622</v>
@@ -13726,19 +13749,19 @@
         <v>2.19</v>
       </c>
       <c r="H115">
-        <v>-0.5466025546016106</v>
+        <v>-0.54660255460161056</v>
       </c>
       <c r="I115">
-        <v>174.3119995117187</v>
+        <v>174.31199951171871</v>
       </c>
       <c r="J115">
         <v>164.8279998779297</v>
       </c>
       <c r="K115">
-        <v>148.4821997070312</v>
+        <v>148.48219970703121</v>
       </c>
       <c r="L115">
-        <v>122.1653499603271</v>
+        <v>122.16534996032711</v>
       </c>
       <c r="M115">
         <v>1.06</v>
@@ -13777,7 +13800,7 @@
         <v>176.75</v>
       </c>
       <c r="Z115">
-        <v>98.93000000000001</v>
+        <v>98.93</v>
       </c>
       <c r="AA115" t="s">
         <v>157</v>
@@ -13818,7 +13841,7 @@
         <v>151</v>
       </c>
       <c r="B116">
-        <v>92.85930867192238</v>
+        <v>92.859308671922378</v>
       </c>
       <c r="C116">
         <v>422</v>
@@ -13830,19 +13853,19 @@
         <v>2.8</v>
       </c>
       <c r="F116">
-        <v>-0.3917966696172515</v>
+        <v>-0.39179666961725151</v>
       </c>
       <c r="G116">
         <v>2.41</v>
       </c>
       <c r="H116">
-        <v>-0.3722172891925176</v>
+        <v>-0.37221728919251762</v>
       </c>
       <c r="I116">
         <v>39.6</v>
       </c>
       <c r="J116">
-        <v>38.72100009918213</v>
+        <v>38.721000099182127</v>
       </c>
       <c r="K116">
         <v>35.92940013885498</v>
@@ -13854,7 +13877,7 @@
         <v>1.02</v>
       </c>
       <c r="N116">
-        <v>1.1</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="P116">
         <v>0</v>
@@ -13899,7 +13922,7 @@
         <v>5.13</v>
       </c>
       <c r="AD116">
-        <v>17.33</v>
+        <v>17.329999999999998</v>
       </c>
       <c r="AE116">
         <v>54.29</v>
@@ -13928,7 +13951,7 @@
         <v>152</v>
       </c>
       <c r="B117">
-        <v>90.767131594906</v>
+        <v>90.767131594906004</v>
       </c>
       <c r="C117">
         <v>3122</v>
@@ -13940,25 +13963,25 @@
         <v>3.09</v>
       </c>
       <c r="F117">
-        <v>-0.2539267494735648</v>
+        <v>-0.25392674947356481</v>
       </c>
       <c r="G117">
         <v>3.2</v>
       </c>
       <c r="H117">
-        <v>0.2539843456855885</v>
+        <v>0.25398434568558848</v>
       </c>
       <c r="I117">
         <v>230.3320007324219</v>
       </c>
       <c r="J117">
-        <v>223.8064987182617</v>
+        <v>223.80649871826171</v>
       </c>
       <c r="K117">
-        <v>195.5907998657227</v>
+        <v>195.59079986572269</v>
       </c>
       <c r="L117">
-        <v>159.1205000686645</v>
+        <v>159.12050006866451</v>
       </c>
       <c r="M117">
         <v>1.03</v>
@@ -14003,7 +14026,7 @@
         <v>38.28</v>
       </c>
       <c r="AB117">
-        <v>8.539999999999999</v>
+        <v>8.5399999999999991</v>
       </c>
       <c r="AC117">
         <v>7.96</v>
@@ -14038,43 +14061,43 @@
         <v>153</v>
       </c>
       <c r="B118">
-        <v>90.37295330503335</v>
+        <v>90.372953305033349</v>
       </c>
       <c r="C118">
         <v>4574</v>
       </c>
       <c r="D118">
-        <v>519.4299999999999</v>
+        <v>519.42999999999995</v>
       </c>
       <c r="E118">
-        <v>2.03</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="F118">
-        <v>-0.7578650782746266</v>
+        <v>-0.75786507827462657</v>
       </c>
       <c r="G118">
-        <v>2.22</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="H118">
-        <v>-0.5228227456821887</v>
+        <v>-0.52282274568218867</v>
       </c>
       <c r="I118">
-        <v>520.83798828125</v>
+        <v>520.83798828124998</v>
       </c>
       <c r="J118">
-        <v>483.4564956665039</v>
+        <v>483.45649566650388</v>
       </c>
       <c r="K118">
         <v>449.4667987060547</v>
       </c>
       <c r="L118">
-        <v>394.82794921875</v>
+        <v>394.82794921875001</v>
       </c>
       <c r="M118">
         <v>1.08</v>
       </c>
       <c r="N118">
-        <v>1.16</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="P118">
         <v>0</v>
@@ -14101,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="X118">
-        <v>281.21</v>
+        <v>281.20999999999998</v>
       </c>
       <c r="Y118">
-        <v>544.08</v>
+        <v>544.08000000000004</v>
       </c>
       <c r="Z118">
         <v>3.65</v>
@@ -14128,7 +14151,7 @@
         <v>1.47</v>
       </c>
       <c r="AG118">
-        <v>-5.1</v>
+        <v>-5.0999999999999996</v>
       </c>
       <c r="AH118" t="s">
         <v>168</v>
@@ -14148,34 +14171,34 @@
         <v>154</v>
       </c>
       <c r="B119">
-        <v>90.79745300181928</v>
+        <v>90.797453001819278</v>
       </c>
       <c r="C119">
         <v>3255</v>
       </c>
       <c r="D119">
-        <v>95.29000000000001</v>
+        <v>95.29</v>
       </c>
       <c r="E119">
         <v>3.09</v>
       </c>
       <c r="F119">
-        <v>-0.2539267494735648</v>
+        <v>-0.25392674947356481</v>
       </c>
       <c r="G119">
         <v>2.48</v>
       </c>
       <c r="H119">
-        <v>-0.3167310683805337</v>
+        <v>-0.31673106838053372</v>
       </c>
       <c r="I119">
-        <v>96.87799987792968</v>
+        <v>96.877999877929682</v>
       </c>
       <c r="J119">
-        <v>94.58300018310547</v>
+        <v>94.583000183105469</v>
       </c>
       <c r="K119">
-        <v>87.035</v>
+        <v>87.034999999999997</v>
       </c>
       <c r="L119">
         <v>72.35124992370605</v>
@@ -14184,7 +14207,7 @@
         <v>1.02</v>
       </c>
       <c r="N119">
-        <v>1.11</v>
+        <v>1.1100000000000001</v>
       </c>
       <c r="P119">
         <v>0</v>
@@ -14217,10 +14240,10 @@
         <v>101.37</v>
       </c>
       <c r="Z119">
-        <v>4.73</v>
+        <v>4.7300000000000004</v>
       </c>
       <c r="AA119">
-        <v>8.460000000000001</v>
+        <v>8.4600000000000009</v>
       </c>
       <c r="AB119">
         <v>3.89</v>
@@ -14235,7 +14258,7 @@
         <v>14.58</v>
       </c>
       <c r="AF119">
-        <v>4.35</v>
+        <v>4.3499999999999996</v>
       </c>
       <c r="AG119">
         <v>19.48</v>
@@ -14250,7 +14273,7 @@
         <v>229</v>
       </c>
       <c r="AK119">
-        <v>9.514747442036944</v>
+        <v>9.5147474420369438</v>
       </c>
     </row>
     <row r="120" spans="1:37">
@@ -14258,7 +14281,7 @@
         <v>155</v>
       </c>
       <c r="B120">
-        <v>93.46573681018799</v>
+        <v>93.465736810187991</v>
       </c>
       <c r="C120">
         <v>2578</v>
@@ -14270,7 +14293,7 @@
         <v>4.21</v>
       </c>
       <c r="F120">
-        <v>0.2785363903917081</v>
+        <v>0.27853639039170808</v>
       </c>
       <c r="G120">
         <v>3.03</v>
@@ -14279,22 +14302,22 @@
         <v>0.1192320951421983</v>
       </c>
       <c r="I120">
-        <v>136.5399963378906</v>
+        <v>136.53999633789061</v>
       </c>
       <c r="J120">
-        <v>131.6524990081787</v>
+        <v>131.65249900817869</v>
       </c>
       <c r="K120">
-        <v>118.6555993652344</v>
+        <v>118.65559936523439</v>
       </c>
       <c r="L120">
-        <v>93.48905006408691</v>
+        <v>93.489050064086911</v>
       </c>
       <c r="M120">
         <v>1.04</v>
       </c>
       <c r="N120">
-        <v>1.15</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="P120">
         <v>0</v>
@@ -14327,13 +14350,13 @@
         <v>144.07</v>
       </c>
       <c r="Z120">
-        <v>10.03</v>
+        <v>10.029999999999999</v>
       </c>
       <c r="AA120">
         <v>31.82</v>
       </c>
       <c r="AB120">
-        <v>2.32</v>
+        <v>2.3199999999999998</v>
       </c>
       <c r="AC120">
         <v>9.84</v>
@@ -14348,7 +14371,7 @@
         <v>33.33</v>
       </c>
       <c r="AG120">
-        <v>-17.24</v>
+        <v>-17.239999999999998</v>
       </c>
       <c r="AH120" t="s">
         <v>178</v>
@@ -14360,10 +14383,11 @@
         <v>236</v>
       </c>
       <c r="AK120">
-        <v>7.194716242124268</v>
+        <v>7.1947162421242679</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>